--- a/Indicator_4/Real_data/Albacore_SAtl.xlsx
+++ b/Indicator_4/Real_data/Albacore_SAtl.xlsx
@@ -1,22 +1,300 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770245B2-B7C2-4DC9-B0F0-1E89AF13C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Albacore_SAtl</t>
+  </si>
+  <si>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>max_age</t>
+  </si>
+  <si>
+    <t>8.559</t>
+  </si>
+  <si>
+    <t>Age to 5% natural survival</t>
+  </si>
+  <si>
+    <t>Life history</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>0.126</t>
+  </si>
+  <si>
+    <t>von Bertalannfy K</t>
+  </si>
+  <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.608</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
+    <t>L50_Linf</t>
+  </si>
+  <si>
+    <t>147.5</t>
+  </si>
+  <si>
+    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+  </si>
+  <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
+    <t>0.758</t>
+  </si>
+  <si>
+    <t>Length at 5% selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Fleet selectivity</t>
+  </si>
+  <si>
+    <t>All fleets combined</t>
+  </si>
+  <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.154</t>
+  </si>
+  <si>
+    <t>Length at full selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
+    <t>0.503</t>
+  </si>
+  <si>
+    <t>Selectivity of maximum length class</t>
+  </si>
+  <si>
+    <t>Fleet_1_L5_L50</t>
+  </si>
+  <si>
+    <t>0.783</t>
+  </si>
+  <si>
+    <t>Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet_1_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Fleet_1_VML</t>
+  </si>
+  <si>
+    <t>0.553</t>
+  </si>
+  <si>
+    <t>Fleet_2_L5_L50</t>
+  </si>
+  <si>
+    <t>0.806</t>
+  </si>
+  <si>
+    <t>Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_2_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.129</t>
+  </si>
+  <si>
+    <t>Fleet_2_VML</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>Fleet_3_L5_L50</t>
+  </si>
+  <si>
+    <t>0.726</t>
+  </si>
+  <si>
+    <t>Fleet 3</t>
+  </si>
+  <si>
+    <t>Fleet_3_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.995</t>
+  </si>
+  <si>
+    <t>Fleet_3_VML</t>
+  </si>
+  <si>
+    <t>0.627</t>
+  </si>
+  <si>
+    <t>Fleet_1_CF</t>
+  </si>
+  <si>
+    <t>0.605</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet catch scale</t>
+  </si>
+  <si>
+    <t>Fleet_2_CF</t>
+  </si>
+  <si>
+    <t>0.153</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_3_CF</t>
+  </si>
+  <si>
+    <t>0.243</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 3</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total_catch</t>
+  </si>
+  <si>
+    <t>Total_mean_len</t>
+  </si>
+  <si>
+    <t>Total_mean_age</t>
+  </si>
+  <si>
+    <t>Total_CV_len</t>
+  </si>
+  <si>
+    <t>Total_frac_mat</t>
+  </si>
+  <si>
+    <t>Total_Index</t>
+  </si>
+  <si>
+    <t>Fleet_1_catch</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_1_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_1_Index</t>
+  </si>
+  <si>
+    <t>Fleet_2_catch</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_2_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_2_Index</t>
+  </si>
+  <si>
+    <t>Fleet_3_catch</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_3_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_3_Index</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +342,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +394,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +428,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +463,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,656 +639,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Albacore_SAtl</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Genus specius</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Billfish</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>North Atlantic</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_age</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8.559</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age to 5% natural survival</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.126</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>von Bertalannfy K</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L50_Linf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.608</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>All_L5_L50</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.758</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.154</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>All_VML</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.503</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fleet_1_L5_L50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.783</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fleet_1_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fleet_1_VML</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.553</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fleet_2_L5_L50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.806</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fleet_2_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.129</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fleet_2_VML</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.018</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fleet_3_L5_L50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.726</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet_3_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.995</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fleet_3_VML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.627</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>All_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fleet_1_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.652</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fleet_2_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.605</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fleet_3_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.632</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fleet_1_CF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.605</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fleet_2_CF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.153</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fleet_3_CF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.243</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1009,138 +1009,92 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_catch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_len</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_age</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total_CV_len</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_frac_mat</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_catch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_len</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_age</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_CV_len</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_frac_mat</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_Index</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_catch</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_len</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_age</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_CV_len</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_frac_mat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_Index</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_catch</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_len</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_age</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_CV_len</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_frac_mat</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1956</v>
       </c>
@@ -1148,16 +1102,16 @@
         <v>21</v>
       </c>
       <c r="C2">
-        <v>106.082</v>
+        <v>106.08199999999999</v>
       </c>
       <c r="E2">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2.342</v>
+        <v>2.3420000000000001</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1166,10 +1120,10 @@
         <v>21</v>
       </c>
       <c r="O2">
-        <v>106.082</v>
+        <v>106.08199999999999</v>
       </c>
       <c r="Q2">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1178,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1957</v>
       </c>
@@ -1189,13 +1143,13 @@
         <v>103.456</v>
       </c>
       <c r="E3">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.397</v>
+        <v>2.3969999999999998</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1207,7 +1161,7 @@
         <v>103.456</v>
       </c>
       <c r="Q3">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1216,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1958</v>
       </c>
@@ -1224,7 +1178,7 @@
         <v>1047</v>
       </c>
       <c r="G4">
-        <v>2.397</v>
+        <v>2.3969999999999998</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1236,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1959</v>
       </c>
@@ -1244,7 +1198,7 @@
         <v>4715</v>
       </c>
       <c r="G5">
-        <v>2.397</v>
+        <v>2.3969999999999998</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1256,7 +1210,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1960</v>
       </c>
@@ -1264,16 +1218,16 @@
         <v>10475</v>
       </c>
       <c r="C6">
-        <v>97.917</v>
+        <v>97.917000000000002</v>
       </c>
       <c r="E6">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="F6">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="G6">
-        <v>2.389</v>
+        <v>2.3889999999999998</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1282,19 +1236,19 @@
         <v>8673</v>
       </c>
       <c r="O6">
-        <v>97.917</v>
+        <v>97.917000000000002</v>
       </c>
       <c r="Q6">
-        <v>0.103</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="R6">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="T6">
         <v>1802</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1961</v>
       </c>
@@ -1302,7 +1256,7 @@
         <v>10765</v>
       </c>
       <c r="G7">
-        <v>2.378</v>
+        <v>2.3780000000000001</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1314,7 +1268,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1962</v>
       </c>
@@ -1328,10 +1282,10 @@
         <v>0.1</v>
       </c>
       <c r="F8">
-        <v>0.889</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="G8">
-        <v>2.329</v>
+        <v>2.3290000000000002</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1346,13 +1300,13 @@
         <v>0.1</v>
       </c>
       <c r="R8">
-        <v>0.889</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="T8">
         <v>2549</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1963</v>
       </c>
@@ -1360,16 +1314,16 @@
         <v>17385</v>
       </c>
       <c r="C9">
-        <v>101.207</v>
+        <v>101.20699999999999</v>
       </c>
       <c r="E9">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="F9">
-        <v>0.966</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="G9">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1378,19 +1332,19 @@
         <v>15104</v>
       </c>
       <c r="O9">
-        <v>101.207</v>
+        <v>101.20699999999999</v>
       </c>
       <c r="Q9">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="R9">
-        <v>0.966</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="T9">
         <v>2281</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1964</v>
       </c>
@@ -1398,16 +1352,16 @@
         <v>25999</v>
       </c>
       <c r="C10">
-        <v>96.849</v>
+        <v>96.849000000000004</v>
       </c>
       <c r="E10">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="F10">
-        <v>0.8080000000000001</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="G10">
-        <v>2.119</v>
+        <v>2.1190000000000002</v>
       </c>
       <c r="H10">
         <v>115</v>
@@ -1416,19 +1370,19 @@
         <v>23738</v>
       </c>
       <c r="O10">
-        <v>96.849</v>
+        <v>96.849000000000004</v>
       </c>
       <c r="Q10">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="R10">
-        <v>0.8080000000000001</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="T10">
         <v>2146</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1965</v>
       </c>
@@ -1439,13 +1393,13 @@
         <v>86.63</v>
       </c>
       <c r="E11">
-        <v>0.118</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="F11">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="G11">
-        <v>1.947</v>
+        <v>1.9470000000000001</v>
       </c>
       <c r="H11">
         <v>346</v>
@@ -1457,16 +1411,16 @@
         <v>86.63</v>
       </c>
       <c r="Q11">
-        <v>0.118</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="R11">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="T11">
         <v>1190</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1966</v>
       </c>
@@ -1474,16 +1428,16 @@
         <v>27296</v>
       </c>
       <c r="C12">
-        <v>87.13500000000001</v>
+        <v>87.135000000000005</v>
       </c>
       <c r="E12">
         <v>0.12</v>
       </c>
       <c r="F12">
-        <v>0.412</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="G12">
-        <v>1.817</v>
+        <v>1.8169999999999999</v>
       </c>
       <c r="H12">
         <v>5275</v>
@@ -1492,19 +1446,19 @@
         <v>21023</v>
       </c>
       <c r="O12">
-        <v>87.13500000000001</v>
+        <v>87.135000000000005</v>
       </c>
       <c r="Q12">
         <v>0.12</v>
       </c>
       <c r="R12">
-        <v>0.412</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="T12">
         <v>998</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1967</v>
       </c>
@@ -1512,10 +1466,10 @@
         <v>15883</v>
       </c>
       <c r="C13">
-        <v>86.786</v>
+        <v>86.786000000000001</v>
       </c>
       <c r="E13">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="F13">
         <v>0.5</v>
@@ -1527,16 +1481,16 @@
         <v>7412</v>
       </c>
       <c r="M13">
-        <v>2.523</v>
+        <v>2.5230000000000001</v>
       </c>
       <c r="N13">
         <v>7719</v>
       </c>
       <c r="O13">
-        <v>86.786</v>
+        <v>86.786000000000001</v>
       </c>
       <c r="Q13">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="R13">
         <v>0.5</v>
@@ -1545,7 +1499,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1968</v>
       </c>
@@ -1553,7 +1507,7 @@
         <v>25688</v>
       </c>
       <c r="C14">
-        <v>83.985</v>
+        <v>83.984999999999999</v>
       </c>
       <c r="E14">
         <v>0.121</v>
@@ -1562,7 +1516,7 @@
         <v>0.252</v>
       </c>
       <c r="G14">
-        <v>1.449</v>
+        <v>1.4490000000000001</v>
       </c>
       <c r="H14">
         <v>12489</v>
@@ -1574,7 +1528,7 @@
         <v>11857</v>
       </c>
       <c r="O14">
-        <v>83.985</v>
+        <v>83.984999999999999</v>
       </c>
       <c r="Q14">
         <v>0.121</v>
@@ -1586,7 +1540,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1969</v>
       </c>
@@ -1600,10 +1554,10 @@
         <v>0.19</v>
       </c>
       <c r="F15">
-        <v>0.646</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="G15">
-        <v>1.348</v>
+        <v>1.3480000000000001</v>
       </c>
       <c r="H15">
         <v>21732</v>
@@ -1615,28 +1569,28 @@
         <v>6331</v>
       </c>
       <c r="O15">
-        <v>88.843</v>
+        <v>88.843000000000004</v>
       </c>
       <c r="Q15">
-        <v>0.118</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="R15">
-        <v>0.601</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="T15">
         <v>430</v>
       </c>
       <c r="U15">
-        <v>88.38200000000001</v>
+        <v>88.382000000000005</v>
       </c>
       <c r="W15">
-        <v>0.261</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="X15">
-        <v>0.6909999999999999</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>0.69099999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1970</v>
       </c>
@@ -1644,16 +1598,16 @@
         <v>23653</v>
       </c>
       <c r="C16">
-        <v>83.77500000000001</v>
+        <v>83.775000000000006</v>
       </c>
       <c r="E16">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="F16">
         <v>0.496</v>
       </c>
       <c r="G16">
-        <v>1.376</v>
+        <v>1.3759999999999999</v>
       </c>
       <c r="H16">
         <v>17255</v>
@@ -1665,28 +1619,28 @@
         <v>5898</v>
       </c>
       <c r="O16">
-        <v>82.935</v>
+        <v>82.935000000000002</v>
       </c>
       <c r="Q16">
         <v>0.153</v>
       </c>
       <c r="R16">
-        <v>0.326</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="T16">
         <v>500</v>
       </c>
       <c r="U16">
-        <v>84.61499999999999</v>
+        <v>84.614999999999995</v>
       </c>
       <c r="W16">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="X16">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1971</v>
       </c>
@@ -1694,16 +1648,16 @@
         <v>24885</v>
       </c>
       <c r="C17">
-        <v>93.851</v>
+        <v>93.850999999999999</v>
       </c>
       <c r="E17">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F17">
-        <v>0.838</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="G17">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="H17">
         <v>21323</v>
@@ -1718,16 +1672,16 @@
         <v>344</v>
       </c>
       <c r="U17">
-        <v>93.851</v>
+        <v>93.850999999999999</v>
       </c>
       <c r="W17">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X17">
-        <v>0.838</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1972</v>
       </c>
@@ -1735,16 +1689,16 @@
         <v>33189</v>
       </c>
       <c r="C18">
-        <v>97.708</v>
+        <v>97.707999999999998</v>
       </c>
       <c r="E18">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="F18">
-        <v>0.958</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="G18">
-        <v>1.215</v>
+        <v>1.2150000000000001</v>
       </c>
       <c r="H18">
         <v>30640</v>
@@ -1759,16 +1713,16 @@
         <v>462</v>
       </c>
       <c r="U18">
-        <v>97.708</v>
+        <v>97.707999999999998</v>
       </c>
       <c r="W18">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="X18">
-        <v>0.958</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>0.95799999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1973</v>
       </c>
@@ -1776,13 +1730,13 @@
         <v>28234.1</v>
       </c>
       <c r="C19">
-        <v>93.098</v>
+        <v>93.097999999999999</v>
       </c>
       <c r="E19">
         <v>0.1</v>
       </c>
       <c r="F19">
-        <v>0.728</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="G19">
         <v>1.147</v>
@@ -1791,16 +1745,16 @@
         <v>25888</v>
       </c>
       <c r="M19">
-        <v>0.979</v>
+        <v>0.97899999999999998</v>
       </c>
       <c r="N19">
         <v>277</v>
       </c>
       <c r="O19">
-        <v>87.973</v>
+        <v>87.972999999999999</v>
       </c>
       <c r="Q19">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="R19">
         <v>0.5</v>
@@ -1809,16 +1763,16 @@
         <v>2069.1</v>
       </c>
       <c r="U19">
-        <v>98.22199999999999</v>
+        <v>98.221999999999994</v>
       </c>
       <c r="W19">
-        <v>0.064</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="X19">
-        <v>0.956</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>0.95599999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1974</v>
       </c>
@@ -1829,10 +1783,10 @@
         <v>94.369</v>
       </c>
       <c r="E20">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="F20">
-        <v>0.831</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="G20">
         <v>1.06</v>
@@ -1841,34 +1795,34 @@
         <v>19079</v>
       </c>
       <c r="M20">
-        <v>1.013</v>
+        <v>1.0129999999999999</v>
       </c>
       <c r="N20">
         <v>109</v>
       </c>
       <c r="O20">
-        <v>91.667</v>
+        <v>91.667000000000002</v>
       </c>
       <c r="Q20">
         <v>0.1</v>
       </c>
       <c r="R20">
-        <v>0.733</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="T20">
         <v>528</v>
       </c>
       <c r="U20">
-        <v>97.072</v>
+        <v>97.072000000000003</v>
       </c>
       <c r="W20">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="X20">
-        <v>0.928</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1975</v>
       </c>
@@ -1876,28 +1830,28 @@
         <v>17607</v>
       </c>
       <c r="C21">
-        <v>90.989</v>
+        <v>90.989000000000004</v>
       </c>
       <c r="E21">
         <v>0.12</v>
       </c>
       <c r="F21">
-        <v>0.631</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="G21">
-        <v>0.903</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="H21">
         <v>16614</v>
       </c>
       <c r="I21">
-        <v>85.161</v>
+        <v>85.161000000000001</v>
       </c>
       <c r="K21">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="L21">
-        <v>0.344</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="M21">
         <v>1.18</v>
@@ -1906,7 +1860,7 @@
         <v>306</v>
       </c>
       <c r="O21">
-        <v>91.038</v>
+        <v>91.037999999999997</v>
       </c>
       <c r="Q21">
         <v>0.152</v>
@@ -1918,16 +1872,16 @@
         <v>687</v>
       </c>
       <c r="U21">
-        <v>96.768</v>
+        <v>96.768000000000001</v>
       </c>
       <c r="W21">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="X21">
-        <v>0.9389999999999999</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>0.93899999999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1976</v>
       </c>
@@ -1935,31 +1889,31 @@
         <v>19375</v>
       </c>
       <c r="C22">
-        <v>94.00700000000001</v>
+        <v>94.007000000000005</v>
       </c>
       <c r="E22">
-        <v>0.117</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="F22">
-        <v>0.729</v>
+        <v>0.72899999999999998</v>
       </c>
       <c r="G22">
-        <v>0.8169999999999999</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="H22">
         <v>17976</v>
       </c>
       <c r="I22">
-        <v>85.65300000000001</v>
+        <v>85.653000000000006</v>
       </c>
       <c r="K22">
-        <v>0.147</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="L22">
         <v>0.41</v>
       </c>
       <c r="M22">
-        <v>1.047</v>
+        <v>1.0469999999999999</v>
       </c>
       <c r="N22">
         <v>73</v>
@@ -1968,7 +1922,7 @@
         <v>102.45</v>
       </c>
       <c r="Q22">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="R22">
         <v>0.91</v>
@@ -1980,16 +1934,16 @@
         <v>1326</v>
       </c>
       <c r="U22">
-        <v>93.91800000000001</v>
+        <v>93.918000000000006</v>
       </c>
       <c r="W22">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X22">
-        <v>0.865</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>0.86499999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1977</v>
       </c>
@@ -1997,28 +1951,28 @@
         <v>21455</v>
       </c>
       <c r="C23">
-        <v>89.056</v>
+        <v>89.055999999999997</v>
       </c>
       <c r="E23">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="F23">
-        <v>0.5620000000000001</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="G23">
-        <v>0.822</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="H23">
         <v>19858</v>
       </c>
       <c r="I23">
-        <v>83.571</v>
+        <v>83.570999999999998</v>
       </c>
       <c r="K23">
         <v>0.156</v>
       </c>
       <c r="L23">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="M23">
         <v>1.222</v>
@@ -2027,22 +1981,22 @@
         <v>105</v>
       </c>
       <c r="O23">
-        <v>94.541</v>
+        <v>94.540999999999997</v>
       </c>
       <c r="Q23">
         <v>0.125</v>
       </c>
       <c r="R23">
-        <v>0.771</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="S23">
-        <v>0.775</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="T23">
         <v>1492</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1978</v>
       </c>
@@ -2050,43 +2004,43 @@
         <v>23095</v>
       </c>
       <c r="C24">
-        <v>89.828</v>
+        <v>89.828000000000003</v>
       </c>
       <c r="E24">
-        <v>0.136</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="F24">
         <v>0.625</v>
       </c>
       <c r="G24">
-        <v>0.845</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="H24">
         <v>21837</v>
       </c>
       <c r="I24">
-        <v>84.63800000000001</v>
+        <v>84.638000000000005</v>
       </c>
       <c r="K24">
-        <v>0.174</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="L24">
-        <v>0.421</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M24">
-        <v>1.112</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="N24">
         <v>135</v>
       </c>
       <c r="O24">
-        <v>90.39700000000001</v>
+        <v>90.397000000000006</v>
       </c>
       <c r="Q24">
         <v>0.154</v>
       </c>
       <c r="R24">
-        <v>0.603</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="S24">
         <v>1.446</v>
@@ -2095,16 +2049,16 @@
         <v>1123</v>
       </c>
       <c r="U24">
-        <v>94.44799999999999</v>
+        <v>94.447999999999993</v>
       </c>
       <c r="W24">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="X24">
-        <v>0.851</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>0.85099999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1979</v>
       </c>
@@ -2112,13 +2066,13 @@
         <v>22640</v>
       </c>
       <c r="C25">
-        <v>90.105</v>
+        <v>90.105000000000004</v>
       </c>
       <c r="E25">
         <v>0.127</v>
       </c>
       <c r="F25">
-        <v>0.613</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="G25">
         <v>0.85</v>
@@ -2130,28 +2084,28 @@
         <v>86.73</v>
       </c>
       <c r="K25">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="L25">
         <v>0.439</v>
       </c>
       <c r="M25">
-        <v>1.108</v>
+        <v>1.1080000000000001</v>
       </c>
       <c r="N25">
         <v>105</v>
       </c>
       <c r="O25">
-        <v>86.923</v>
+        <v>86.923000000000002</v>
       </c>
       <c r="Q25">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="R25">
         <v>0.5</v>
       </c>
       <c r="S25">
-        <v>0.584</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="T25">
         <v>1317</v>
@@ -2160,13 +2114,13 @@
         <v>96.66</v>
       </c>
       <c r="W25">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="X25">
-        <v>0.901</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>0.90100000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1980</v>
       </c>
@@ -2177,19 +2131,19 @@
         <v>91.872</v>
       </c>
       <c r="E26">
-        <v>0.133</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="F26">
-        <v>0.641</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="G26">
-        <v>0.844</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="H26">
         <v>19400</v>
       </c>
       <c r="I26">
-        <v>81.226</v>
+        <v>81.225999999999999</v>
       </c>
       <c r="K26">
         <v>0.193</v>
@@ -2198,19 +2152,19 @@
         <v>0.315</v>
       </c>
       <c r="M26">
-        <v>1.136</v>
+        <v>1.1359999999999999</v>
       </c>
       <c r="N26">
         <v>333</v>
       </c>
       <c r="O26">
-        <v>90.09099999999999</v>
+        <v>90.090999999999994</v>
       </c>
       <c r="Q26">
         <v>0.152</v>
       </c>
       <c r="R26">
-        <v>0.5639999999999999</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="S26">
         <v>0.871</v>
@@ -2219,16 +2173,16 @@
         <v>3213</v>
       </c>
       <c r="U26">
-        <v>98.086</v>
+        <v>98.085999999999999</v>
       </c>
       <c r="W26">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="X26">
-        <v>0.843</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>0.84299999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1981</v>
       </c>
@@ -2236,31 +2190,31 @@
         <v>24040</v>
       </c>
       <c r="C27">
-        <v>95.765</v>
+        <v>95.765000000000001</v>
       </c>
       <c r="E27">
-        <v>0.118</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="F27">
-        <v>0.756</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="G27">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="H27">
         <v>18869</v>
       </c>
       <c r="I27">
-        <v>89.547</v>
+        <v>89.546999999999997</v>
       </c>
       <c r="K27">
         <v>0.189</v>
       </c>
       <c r="L27">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="M27">
-        <v>1.007</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="N27">
         <v>558</v>
@@ -2269,10 +2223,10 @@
         <v>91.36</v>
       </c>
       <c r="Q27">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="R27">
-        <v>0.5610000000000001</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="S27">
         <v>1.853</v>
@@ -2284,13 +2238,13 @@
         <v>101.077</v>
       </c>
       <c r="W27">
-        <v>0.074</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="X27">
-        <v>0.9419999999999999</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>0.94199999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1982</v>
       </c>
@@ -2301,43 +2255,43 @@
         <v>93.637</v>
       </c>
       <c r="E28">
-        <v>0.168</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="F28">
-        <v>0.639</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="G28">
-        <v>0.828</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="H28">
         <v>23363</v>
       </c>
       <c r="I28">
-        <v>86.194</v>
+        <v>86.194000000000003</v>
       </c>
       <c r="K28">
         <v>0.17</v>
       </c>
       <c r="L28">
-        <v>0.422</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="M28">
-        <v>0.984</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="N28">
         <v>569</v>
       </c>
       <c r="O28">
-        <v>87.922</v>
+        <v>87.921999999999997</v>
       </c>
       <c r="Q28">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="R28">
-        <v>0.506</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="S28">
-        <v>1.436</v>
+        <v>1.4359999999999999</v>
       </c>
       <c r="T28">
         <v>5740</v>
@@ -2346,13 +2300,13 @@
         <v>100.217</v>
       </c>
       <c r="W28">
-        <v>0.147</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="X28">
-        <v>0.8129999999999999</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>0.81299999999999994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1983</v>
       </c>
@@ -2360,7 +2314,7 @@
         <v>14918</v>
       </c>
       <c r="C29">
-        <v>97.345</v>
+        <v>97.344999999999999</v>
       </c>
       <c r="E29">
         <v>0.108</v>
@@ -2369,37 +2323,37 @@
         <v>0.82</v>
       </c>
       <c r="G29">
-        <v>0.819</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="H29">
         <v>10101</v>
       </c>
       <c r="I29">
-        <v>88.04300000000001</v>
+        <v>88.043000000000006</v>
       </c>
       <c r="K29">
         <v>0.189</v>
       </c>
       <c r="L29">
-        <v>0.479</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="M29">
-        <v>0.9429999999999999</v>
+        <v>0.94299999999999995</v>
       </c>
       <c r="N29">
         <v>162</v>
       </c>
       <c r="O29">
-        <v>97.708</v>
+        <v>97.707999999999998</v>
       </c>
       <c r="Q29">
         <v>0.113</v>
       </c>
       <c r="R29">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="S29">
-        <v>1.168</v>
+        <v>1.1679999999999999</v>
       </c>
       <c r="T29">
         <v>4655</v>
@@ -2408,16 +2362,16 @@
         <v>100.324</v>
       </c>
       <c r="W29">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="X29">
-        <v>0.929</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Y29">
-        <v>1.689</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>1.6890000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1984</v>
       </c>
@@ -2425,13 +2379,13 @@
         <v>14599</v>
       </c>
       <c r="C30">
-        <v>96.952</v>
+        <v>96.951999999999998</v>
       </c>
       <c r="E30">
         <v>0.115</v>
       </c>
       <c r="F30">
-        <v>0.8139999999999999</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="G30">
         <v>0.79</v>
@@ -2440,16 +2394,16 @@
         <v>8237</v>
       </c>
       <c r="I30">
-        <v>94.60899999999999</v>
+        <v>94.608999999999995</v>
       </c>
       <c r="K30">
         <v>0.19</v>
       </c>
       <c r="L30">
-        <v>0.605</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="M30">
-        <v>1.084</v>
+        <v>1.0840000000000001</v>
       </c>
       <c r="N30">
         <v>224</v>
@@ -2461,7 +2415,7 @@
         <v>0.114</v>
       </c>
       <c r="R30">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="S30">
         <v>1.169</v>
@@ -2470,19 +2424,19 @@
         <v>6138</v>
       </c>
       <c r="U30">
-        <v>97.98699999999999</v>
+        <v>97.986999999999995</v>
       </c>
       <c r="W30">
-        <v>0.091</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="X30">
-        <v>0.885</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="Y30">
-        <v>1.459</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>1.4590000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1985</v>
       </c>
@@ -2496,49 +2450,49 @@
         <v>0.155</v>
       </c>
       <c r="F31">
-        <v>0.466</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="G31">
-        <v>0.702</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="H31">
         <v>20154</v>
       </c>
       <c r="I31">
-        <v>83.223</v>
+        <v>83.222999999999999</v>
       </c>
       <c r="K31">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="L31">
-        <v>0.361</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="M31">
-        <v>0.989</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="N31">
         <v>623</v>
       </c>
       <c r="O31">
-        <v>91.351</v>
+        <v>91.350999999999999</v>
       </c>
       <c r="Q31">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="R31">
-        <v>0.649</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="S31">
         <v>2.032</v>
       </c>
       <c r="T31">
-        <v>10320.3</v>
+        <v>10320.299999999999</v>
       </c>
       <c r="U31">
-        <v>86.20399999999999</v>
+        <v>86.203999999999994</v>
       </c>
       <c r="W31">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X31">
         <v>0.44</v>
@@ -2547,7 +2501,7 @@
         <v>1.526</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1986</v>
       </c>
@@ -2555,13 +2509,13 @@
         <v>37288</v>
       </c>
       <c r="C32">
-        <v>90.203</v>
+        <v>90.203000000000003</v>
       </c>
       <c r="E32">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="F32">
-        <v>0.589</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="G32">
         <v>0.746</v>
@@ -2570,49 +2524,49 @@
         <v>27913</v>
       </c>
       <c r="I32">
-        <v>85.01900000000001</v>
+        <v>85.019000000000005</v>
       </c>
       <c r="K32">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="L32">
-        <v>0.402</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="M32">
-        <v>0.984</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="N32">
         <v>739</v>
       </c>
       <c r="O32">
-        <v>97.143</v>
+        <v>97.143000000000001</v>
       </c>
       <c r="Q32">
         <v>0.104</v>
       </c>
       <c r="R32">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="S32">
-        <v>2.503</v>
+        <v>2.5030000000000001</v>
       </c>
       <c r="T32">
         <v>8636</v>
       </c>
       <c r="U32">
-        <v>89.617</v>
+        <v>89.617000000000004</v>
       </c>
       <c r="W32">
-        <v>0.136</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="X32">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="Y32">
-        <v>1.509</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>1.5089999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1987</v>
       </c>
@@ -2620,55 +2574,55 @@
         <v>40630</v>
       </c>
       <c r="C33">
-        <v>89.65000000000001</v>
+        <v>89.65</v>
       </c>
       <c r="E33">
         <v>0.109</v>
       </c>
       <c r="F33">
-        <v>0.5620000000000001</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="G33">
-        <v>0.8080000000000001</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="H33">
         <v>29173</v>
       </c>
       <c r="I33">
-        <v>83.667</v>
+        <v>83.667000000000002</v>
       </c>
       <c r="K33">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="L33">
-        <v>0.363</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="M33">
-        <v>0.822</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="N33">
         <v>357</v>
       </c>
       <c r="O33">
-        <v>99.167</v>
+        <v>99.167000000000002</v>
       </c>
       <c r="Q33">
-        <v>0.083</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="R33">
-        <v>0.944</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="S33">
-        <v>0.982</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="T33">
         <v>11100</v>
       </c>
       <c r="U33">
-        <v>88.473</v>
+        <v>88.472999999999999</v>
       </c>
       <c r="W33">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="X33">
         <v>0.501</v>
@@ -2677,7 +2631,7 @@
         <v>1.411</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1988</v>
       </c>
@@ -2685,81 +2639,81 @@
         <v>30173</v>
       </c>
       <c r="C34">
-        <v>88.877</v>
+        <v>88.876999999999995</v>
       </c>
       <c r="E34">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="F34">
         <v>0.51</v>
       </c>
       <c r="G34">
-        <v>0.741</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="H34">
         <v>20926</v>
       </c>
       <c r="I34">
-        <v>89.599</v>
+        <v>89.599000000000004</v>
       </c>
       <c r="K34">
         <v>0.152</v>
       </c>
       <c r="L34">
-        <v>0.486</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="M34">
-        <v>0.663</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="N34">
         <v>405</v>
       </c>
       <c r="O34">
-        <v>96.842</v>
+        <v>96.841999999999999</v>
       </c>
       <c r="Q34">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="R34">
-        <v>0.737</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="S34">
-        <v>0.6889999999999999</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="T34">
         <v>8842</v>
       </c>
       <c r="U34">
-        <v>85.98099999999999</v>
+        <v>85.980999999999995</v>
       </c>
       <c r="W34">
-        <v>0.132</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="X34">
         <v>0.443</v>
       </c>
       <c r="Y34">
-        <v>1.467</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>1.4670000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1989</v>
       </c>
       <c r="B35">
-        <v>27211.6</v>
+        <v>27211.599999999999</v>
       </c>
       <c r="C35">
-        <v>89.15300000000001</v>
+        <v>89.153000000000006</v>
       </c>
       <c r="E35">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="F35">
-        <v>0.522</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="G35">
-        <v>0.643</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="H35">
         <v>18440</v>
@@ -2768,28 +2722,28 @@
         <v>88.52</v>
       </c>
       <c r="K35">
-        <v>0.139</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="L35">
-        <v>0.541</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="M35">
-        <v>0.576</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="N35">
         <v>450</v>
       </c>
       <c r="O35">
-        <v>97.30800000000001</v>
+        <v>97.308000000000007</v>
       </c>
       <c r="Q35">
         <v>0.122</v>
       </c>
       <c r="R35">
-        <v>0.8080000000000001</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="S35">
-        <v>0.859</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="T35">
         <v>8321.6</v>
@@ -2807,7 +2761,7 @@
         <v>1.754</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1990</v>
       </c>
@@ -2815,22 +2769,22 @@
         <v>28714</v>
       </c>
       <c r="C36">
-        <v>88.048</v>
+        <v>88.048000000000002</v>
       </c>
       <c r="E36">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="F36">
-        <v>0.485</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="G36">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="H36">
         <v>20461</v>
       </c>
       <c r="I36">
-        <v>85.19499999999999</v>
+        <v>85.194999999999993</v>
       </c>
       <c r="K36">
         <v>0.122</v>
@@ -2839,19 +2793,19 @@
         <v>0.43</v>
       </c>
       <c r="M36">
-        <v>0.586</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="N36">
         <v>587</v>
       </c>
       <c r="O36">
-        <v>97.60899999999999</v>
+        <v>97.608999999999995</v>
       </c>
       <c r="Q36">
-        <v>0.133</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="R36">
-        <v>0.783</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="S36">
         <v>1.175</v>
@@ -2860,19 +2814,19 @@
         <v>7666</v>
       </c>
       <c r="U36">
-        <v>81.34099999999999</v>
+        <v>81.340999999999994</v>
       </c>
       <c r="W36">
         <v>0.193</v>
       </c>
       <c r="X36">
-        <v>0.244</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="Y36">
-        <v>1.148</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>1.1479999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1991</v>
       </c>
@@ -2886,37 +2840,37 @@
         <v>0.129</v>
       </c>
       <c r="F37">
-        <v>0.359</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="G37">
-        <v>0.507</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="H37">
         <v>19914</v>
       </c>
       <c r="I37">
-        <v>74.839</v>
+        <v>74.838999999999999</v>
       </c>
       <c r="K37">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.633</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="N37">
         <v>804.4</v>
       </c>
       <c r="O37">
-        <v>96.667</v>
+        <v>96.667000000000002</v>
       </c>
       <c r="Q37">
         <v>0.106</v>
       </c>
       <c r="R37">
-        <v>0.852</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="S37">
         <v>1.343</v>
@@ -2925,19 +2879,19 @@
         <v>5297.7</v>
       </c>
       <c r="U37">
-        <v>83.871</v>
+        <v>83.870999999999995</v>
       </c>
       <c r="W37">
-        <v>0.212</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="X37">
-        <v>0.226</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="Y37">
         <v>1.333</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1992</v>
       </c>
@@ -2945,7 +2899,7 @@
         <v>36564</v>
       </c>
       <c r="C38">
-        <v>92.496</v>
+        <v>92.495999999999995</v>
       </c>
       <c r="E38">
         <v>0.13</v>
@@ -2960,22 +2914,22 @@
         <v>23068</v>
       </c>
       <c r="I38">
-        <v>89.663</v>
+        <v>89.662999999999997</v>
       </c>
       <c r="K38">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="L38">
-        <v>0.523</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="M38">
-        <v>0.727</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="N38">
         <v>1000.9</v>
       </c>
       <c r="O38">
-        <v>90.429</v>
+        <v>90.429000000000002</v>
       </c>
       <c r="Q38">
         <v>0.154</v>
@@ -2984,57 +2938,57 @@
         <v>0.6</v>
       </c>
       <c r="S38">
-        <v>0.727</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="T38">
         <v>12495.1</v>
       </c>
       <c r="U38">
-        <v>94.94499999999999</v>
+        <v>94.944999999999993</v>
       </c>
       <c r="W38">
         <v>0.113</v>
       </c>
       <c r="X38">
-        <v>0.6889999999999999</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="Y38">
-        <v>0.884</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>0.88400000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1993</v>
       </c>
       <c r="B39">
-        <v>32814.3</v>
+        <v>32814.300000000003</v>
       </c>
       <c r="C39">
-        <v>88.801</v>
+        <v>88.801000000000002</v>
       </c>
       <c r="E39">
-        <v>0.139</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="F39">
-        <v>0.531</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="G39">
-        <v>0.538</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="H39">
         <v>19420</v>
       </c>
       <c r="I39">
-        <v>84.224</v>
+        <v>84.224000000000004</v>
       </c>
       <c r="K39">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="L39">
-        <v>0.404</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="M39">
-        <v>0.769</v>
+        <v>0.76900000000000002</v>
       </c>
       <c r="N39">
         <v>748.5</v>
@@ -3043,10 +2997,10 @@
         <v>88.69</v>
       </c>
       <c r="Q39">
-        <v>0.133</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="R39">
-        <v>0.571</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="S39">
         <v>0.62</v>
@@ -3055,19 +3009,19 @@
         <v>12645.8</v>
       </c>
       <c r="U39">
-        <v>91.145</v>
+        <v>91.144999999999996</v>
       </c>
       <c r="W39">
         <v>0.124</v>
       </c>
       <c r="X39">
-        <v>0.575</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="Y39">
         <v>1.546</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1994</v>
       </c>
@@ -3081,10 +3035,10 @@
         <v>0.15</v>
       </c>
       <c r="F40">
-        <v>0.492</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="G40">
-        <v>0.575</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="H40">
         <v>22575.8</v>
@@ -3093,7 +3047,7 @@
         <v>83.88</v>
       </c>
       <c r="K40">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="L40">
         <v>0.443</v>
@@ -3114,13 +3068,13 @@
         <v>0.52</v>
       </c>
       <c r="S40">
-        <v>0.846</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="T40">
         <v>11801.2</v>
       </c>
       <c r="U40">
-        <v>88.059</v>
+        <v>88.058999999999997</v>
       </c>
       <c r="W40">
         <v>0.122</v>
@@ -3129,36 +3083,36 @@
         <v>0.502</v>
       </c>
       <c r="Y40">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1995</v>
       </c>
       <c r="B41">
-        <v>27553.6</v>
+        <v>27553.599999999999</v>
       </c>
       <c r="C41">
-        <v>85.121</v>
+        <v>85.120999999999995</v>
       </c>
       <c r="E41">
-        <v>0.169</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="F41">
-        <v>0.399</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="G41">
-        <v>0.533</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="H41">
         <v>18354.3</v>
       </c>
       <c r="I41">
-        <v>90.595</v>
+        <v>90.594999999999999</v>
       </c>
       <c r="K41">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="L41">
         <v>0.626</v>
@@ -3170,51 +3124,51 @@
         <v>695.5</v>
       </c>
       <c r="S41">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="T41">
-        <v>8503.799999999999</v>
+        <v>8503.7999999999993</v>
       </c>
       <c r="U41">
-        <v>79.64700000000001</v>
+        <v>79.647000000000006</v>
       </c>
       <c r="W41">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="X41">
-        <v>0.171</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="Y41">
         <v>1.103</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1996</v>
       </c>
       <c r="B42">
-        <v>28426.4</v>
+        <v>28426.400000000001</v>
       </c>
       <c r="C42">
-        <v>82.343</v>
+        <v>82.343000000000004</v>
       </c>
       <c r="E42">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F42">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="G42">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="H42">
         <v>18974</v>
       </c>
       <c r="I42">
-        <v>79.06699999999999</v>
+        <v>79.066999999999993</v>
       </c>
       <c r="K42">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="L42">
         <v>0.221</v>
@@ -3229,7 +3183,7 @@
         <v>87.5</v>
       </c>
       <c r="Q42">
-        <v>0.239</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="R42">
         <v>0.5</v>
@@ -3241,7 +3195,7 @@
         <v>8667</v>
       </c>
       <c r="U42">
-        <v>80.462</v>
+        <v>80.462000000000003</v>
       </c>
       <c r="W42">
         <v>0.114</v>
@@ -3250,10 +3204,10 @@
         <v>0.125</v>
       </c>
       <c r="Y42">
-        <v>1.511</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>1.5109999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1997</v>
       </c>
@@ -3261,31 +3215,31 @@
         <v>28022.3</v>
       </c>
       <c r="C43">
-        <v>91.004</v>
+        <v>91.004000000000005</v>
       </c>
       <c r="E43">
         <v>0.155</v>
       </c>
       <c r="F43">
-        <v>0.552</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="G43">
-        <v>0.478</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="H43">
         <v>18169</v>
       </c>
       <c r="I43">
-        <v>93.271</v>
+        <v>93.271000000000001</v>
       </c>
       <c r="K43">
         <v>0.184</v>
       </c>
       <c r="L43">
-        <v>0.662</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="M43">
-        <v>1.055</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="N43">
         <v>672.8</v>
@@ -3300,7 +3254,7 @@
         <v>0.6</v>
       </c>
       <c r="S43">
-        <v>0.791</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="T43">
         <v>9180.5</v>
@@ -3312,13 +3266,13 @@
         <v>0.122</v>
       </c>
       <c r="X43">
-        <v>0.472</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="Y43">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1998</v>
       </c>
@@ -3326,120 +3280,120 @@
         <v>30595</v>
       </c>
       <c r="C44">
-        <v>89.345</v>
+        <v>89.344999999999999</v>
       </c>
       <c r="E44">
         <v>0.13</v>
       </c>
       <c r="F44">
-        <v>0.548</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="G44">
-        <v>0.527</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="H44">
         <v>16113</v>
       </c>
       <c r="I44">
-        <v>95.474</v>
+        <v>95.474000000000004</v>
       </c>
       <c r="K44">
         <v>0.157</v>
       </c>
       <c r="L44">
-        <v>0.733</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="M44">
-        <v>0.905</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="N44">
         <v>486.9</v>
       </c>
       <c r="S44">
-        <v>0.729</v>
+        <v>0.72899999999999998</v>
       </c>
       <c r="T44">
         <v>13995.1</v>
       </c>
       <c r="U44">
-        <v>86.28100000000001</v>
+        <v>86.281000000000006</v>
       </c>
       <c r="W44">
-        <v>0.116</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="X44">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="Y44">
         <v>1.532</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1999</v>
       </c>
       <c r="B45">
-        <v>27656.4</v>
+        <v>27656.400000000001</v>
       </c>
       <c r="C45">
-        <v>89.81399999999999</v>
+        <v>89.813999999999993</v>
       </c>
       <c r="E45">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="F45">
-        <v>0.542</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="G45">
-        <v>0.582</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="H45">
         <v>17390.8</v>
       </c>
       <c r="I45">
-        <v>98.877</v>
+        <v>98.876999999999995</v>
       </c>
       <c r="K45">
         <v>0.151</v>
       </c>
       <c r="L45">
-        <v>0.797</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="M45">
-        <v>0.738</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="N45">
         <v>1559.5</v>
       </c>
       <c r="O45">
-        <v>90.19199999999999</v>
+        <v>90.191999999999993</v>
       </c>
       <c r="Q45">
         <v>0.16</v>
       </c>
       <c r="R45">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="S45">
-        <v>0.838</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="T45">
         <v>8706.1</v>
       </c>
       <c r="U45">
-        <v>85.093</v>
+        <v>85.093000000000004</v>
       </c>
       <c r="W45">
-        <v>0.131</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="X45">
-        <v>0.396</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="Y45">
-        <v>1.217</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>1.2170000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2000</v>
       </c>
@@ -3447,10 +3401,10 @@
         <v>31387.9</v>
       </c>
       <c r="C46">
-        <v>93.90300000000001</v>
+        <v>93.903000000000006</v>
       </c>
       <c r="E46">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="F46">
         <v>0.626</v>
@@ -3468,10 +3422,10 @@
         <v>0.158</v>
       </c>
       <c r="L46">
-        <v>0.732</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="M46">
-        <v>0.643</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="N46">
         <v>3041.1</v>
@@ -3492,19 +3446,19 @@
         <v>11107.5</v>
       </c>
       <c r="U46">
-        <v>94.048</v>
+        <v>94.048000000000002</v>
       </c>
       <c r="W46">
         <v>0.184</v>
       </c>
       <c r="X46">
-        <v>0.667</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="Y46">
         <v>0.97</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2001</v>
       </c>
@@ -3512,16 +3466,16 @@
         <v>38795.5</v>
       </c>
       <c r="C47">
-        <v>90.10899999999999</v>
+        <v>90.108999999999995</v>
       </c>
       <c r="E47">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="F47">
-        <v>0.516</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="G47">
-        <v>0.598</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="H47">
         <v>15834.4</v>
@@ -3530,46 +3484,46 @@
         <v>104.008</v>
       </c>
       <c r="K47">
-        <v>0.091</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="L47">
-        <v>0.961</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="M47">
-        <v>0.735</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="N47">
         <v>5235.2</v>
       </c>
       <c r="O47">
-        <v>84.595</v>
+        <v>84.594999999999999</v>
       </c>
       <c r="Q47">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="R47">
-        <v>0.405</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="S47">
         <v>1.371</v>
       </c>
       <c r="T47">
-        <v>17725.9</v>
+        <v>17725.900000000001</v>
       </c>
       <c r="U47">
-        <v>85.917</v>
+        <v>85.917000000000002</v>
       </c>
       <c r="W47">
         <v>0.155</v>
       </c>
       <c r="X47">
-        <v>0.348</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="Y47">
-        <v>0.5639999999999999</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>0.56399999999999995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2002</v>
       </c>
@@ -3580,43 +3534,43 @@
         <v>84.7</v>
       </c>
       <c r="E48">
-        <v>0.212</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="F48">
         <v>0.501</v>
       </c>
       <c r="G48">
-        <v>0.5669999999999999</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="H48">
         <v>17321</v>
       </c>
       <c r="I48">
-        <v>92.06999999999999</v>
+        <v>92.07</v>
       </c>
       <c r="K48">
-        <v>0.174</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="L48">
-        <v>0.632</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="M48">
-        <v>0.546</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="N48">
-        <v>1142.4</v>
+        <v>1142.4000000000001</v>
       </c>
       <c r="O48">
-        <v>69.73699999999999</v>
+        <v>69.736999999999995</v>
       </c>
       <c r="Q48">
         <v>0.307</v>
       </c>
       <c r="R48">
-        <v>0.237</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="S48">
-        <v>0.852</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="T48">
         <v>13282.3</v>
@@ -3628,13 +3582,13 @@
         <v>0.184</v>
       </c>
       <c r="X48">
-        <v>0.5669999999999999</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="Y48">
-        <v>0.455</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>0.45500000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2003</v>
       </c>
@@ -3642,28 +3596,28 @@
         <v>28004.6</v>
       </c>
       <c r="C49">
-        <v>90.18300000000001</v>
+        <v>90.183000000000007</v>
       </c>
       <c r="E49">
-        <v>0.169</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="F49">
-        <v>0.644</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="G49">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="H49">
         <v>17356</v>
       </c>
       <c r="I49">
-        <v>97.914</v>
+        <v>97.914000000000001</v>
       </c>
       <c r="K49">
         <v>0.128</v>
       </c>
       <c r="L49">
-        <v>0.827</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="M49">
         <v>0.495</v>
@@ -3672,51 +3626,51 @@
         <v>533.6</v>
       </c>
       <c r="O49">
-        <v>70.526</v>
+        <v>70.525999999999996</v>
       </c>
       <c r="Q49">
         <v>0.27</v>
       </c>
       <c r="R49">
-        <v>0.211</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="S49">
-        <v>0.896</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="T49">
         <v>10115</v>
       </c>
       <c r="U49">
-        <v>96.146</v>
+        <v>96.146000000000001</v>
       </c>
       <c r="W49">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X49">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="Y49">
         <v>0.317</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2004</v>
       </c>
       <c r="B50">
-        <v>22544.8</v>
+        <v>22544.799999999999</v>
       </c>
       <c r="C50">
-        <v>88.396</v>
+        <v>88.396000000000001</v>
       </c>
       <c r="E50">
         <v>0.18</v>
       </c>
       <c r="F50">
-        <v>0.527</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="G50">
-        <v>0.428</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="H50">
         <v>13325</v>
@@ -3725,46 +3679,46 @@
         <v>94.12</v>
       </c>
       <c r="K50">
-        <v>0.131</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="L50">
-        <v>0.6909999999999999</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="M50">
-        <v>0.851</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="N50">
         <v>703.3</v>
       </c>
       <c r="O50">
-        <v>76.786</v>
+        <v>76.786000000000001</v>
       </c>
       <c r="Q50">
-        <v>0.268</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="R50">
-        <v>0.321</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="S50">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="T50">
         <v>8516.5</v>
       </c>
       <c r="U50">
-        <v>91.339</v>
+        <v>91.338999999999999</v>
       </c>
       <c r="W50">
         <v>0.16</v>
       </c>
       <c r="X50">
-        <v>0.547</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="Y50">
-        <v>0.229</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>0.22900000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2005</v>
       </c>
@@ -3772,22 +3726,22 @@
         <v>18881.5</v>
       </c>
       <c r="C51">
-        <v>91.233</v>
+        <v>91.233000000000004</v>
       </c>
       <c r="E51">
         <v>0.157</v>
       </c>
       <c r="F51">
-        <v>0.569</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="G51">
-        <v>0.428</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="H51">
         <v>10772</v>
       </c>
       <c r="I51">
-        <v>94.07299999999999</v>
+        <v>94.072999999999993</v>
       </c>
       <c r="K51">
         <v>0.125</v>
@@ -3796,63 +3750,63 @@
         <v>0.7</v>
       </c>
       <c r="M51">
-        <v>0.8169999999999999</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="N51">
         <v>1446.1</v>
       </c>
       <c r="S51">
-        <v>0.727</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="T51">
         <v>6663.4</v>
       </c>
       <c r="U51">
-        <v>89.81399999999999</v>
+        <v>89.813999999999993</v>
       </c>
       <c r="W51">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="X51">
         <v>0.504</v>
       </c>
       <c r="Y51">
-        <v>0.145</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2006</v>
       </c>
       <c r="B52">
-        <v>24452.8</v>
+        <v>24452.799999999999</v>
       </c>
       <c r="C52">
-        <v>90.892</v>
+        <v>90.891999999999996</v>
       </c>
       <c r="E52">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="F52">
-        <v>0.612</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="G52">
-        <v>0.451</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="H52">
         <v>12359</v>
       </c>
       <c r="I52">
-        <v>91.45699999999999</v>
+        <v>91.456999999999994</v>
       </c>
       <c r="K52">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="L52">
-        <v>0.597</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="M52">
-        <v>0.661</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="N52">
         <v>2247.1</v>
@@ -3861,22 +3815,22 @@
         <v>0.41</v>
       </c>
       <c r="T52">
-        <v>9846.700000000001</v>
+        <v>9846.7000000000007</v>
       </c>
       <c r="U52">
         <v>90.61</v>
       </c>
       <c r="W52">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="X52">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="Y52">
-        <v>0.5610000000000001</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>0.56100000000000005</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2007</v>
       </c>
@@ -3884,96 +3838,96 @@
         <v>20283</v>
       </c>
       <c r="C53">
-        <v>86.751</v>
+        <v>86.751000000000005</v>
       </c>
       <c r="E53">
         <v>0.159</v>
       </c>
       <c r="F53">
-        <v>0.456</v>
+        <v>0.45600000000000002</v>
       </c>
       <c r="G53">
-        <v>0.487</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="H53">
         <v>13202</v>
       </c>
       <c r="I53">
-        <v>90.319</v>
+        <v>90.319000000000003</v>
       </c>
       <c r="K53">
         <v>0.153</v>
       </c>
       <c r="L53">
-        <v>0.579</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="M53">
-        <v>0.833</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="N53">
         <v>1313.5</v>
       </c>
       <c r="O53">
-        <v>87.083</v>
+        <v>87.082999999999998</v>
       </c>
       <c r="Q53">
         <v>0.186</v>
       </c>
       <c r="R53">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="S53">
-        <v>0.351</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="T53">
         <v>5767.5</v>
       </c>
       <c r="U53">
-        <v>84.801</v>
+        <v>84.801000000000002</v>
       </c>
       <c r="W53">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="X53">
-        <v>0.414</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="Y53">
-        <v>0.706</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>0.70599999999999996</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2008</v>
       </c>
       <c r="B54">
-        <v>18867.4</v>
+        <v>18867.400000000001</v>
       </c>
       <c r="C54">
-        <v>89.01900000000001</v>
+        <v>89.019000000000005</v>
       </c>
       <c r="E54">
         <v>0.157</v>
       </c>
       <c r="F54">
-        <v>0.484</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="G54">
-        <v>0.514</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="H54">
-        <v>10054.2</v>
+        <v>10054.200000000001</v>
       </c>
       <c r="I54">
-        <v>88.051</v>
+        <v>88.051000000000002</v>
       </c>
       <c r="K54">
         <v>0.153</v>
       </c>
       <c r="L54">
-        <v>0.487</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="M54">
-        <v>0.902</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="N54">
         <v>2632.8</v>
@@ -3982,13 +3936,13 @@
         <v>94</v>
       </c>
       <c r="Q54">
-        <v>0.202</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="R54">
-        <v>0.467</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="S54">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="T54">
         <v>6180.4</v>
@@ -3997,16 +3951,16 @@
         <v>87.012</v>
       </c>
       <c r="W54">
-        <v>0.136</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="X54">
-        <v>0.491</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="Y54">
-        <v>0.531</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>0.53100000000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2009</v>
       </c>
@@ -4014,16 +3968,16 @@
         <v>22248.3</v>
       </c>
       <c r="C55">
-        <v>92.086</v>
+        <v>92.085999999999999</v>
       </c>
       <c r="E55">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="F55">
         <v>0.61</v>
       </c>
       <c r="G55">
-        <v>0.476</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="H55">
         <v>9052</v>
@@ -4032,13 +3986,13 @@
         <v>90.863</v>
       </c>
       <c r="K55">
-        <v>0.133</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="L55">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M55">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="N55">
         <v>2470.4</v>
@@ -4047,63 +4001,63 @@
         <v>100.851</v>
       </c>
       <c r="Q55">
-        <v>0.089</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="R55">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="S55">
-        <v>0.8159999999999999</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="T55">
         <v>10725.9</v>
       </c>
       <c r="U55">
-        <v>88.315</v>
+        <v>88.314999999999998</v>
       </c>
       <c r="W55">
         <v>0.157</v>
       </c>
       <c r="X55">
-        <v>0.468</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="Y55">
-        <v>0.671</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>0.67100000000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2010</v>
       </c>
       <c r="B56">
-        <v>19224.6</v>
+        <v>19224.599999999999</v>
       </c>
       <c r="C56">
-        <v>91.075</v>
+        <v>91.075000000000003</v>
       </c>
       <c r="E56">
-        <v>0.133</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="F56">
-        <v>0.5590000000000001</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="G56">
-        <v>0.488</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="H56">
         <v>11104.7</v>
       </c>
       <c r="I56">
-        <v>93.02500000000001</v>
+        <v>93.025000000000006</v>
       </c>
       <c r="K56">
         <v>0.15</v>
       </c>
       <c r="L56">
-        <v>0.614</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="M56">
-        <v>1.029</v>
+        <v>1.0289999999999999</v>
       </c>
       <c r="N56">
         <v>1693.2</v>
@@ -4112,31 +4066,31 @@
         <v>101.429</v>
       </c>
       <c r="Q56">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="R56">
-        <v>0.952</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="S56">
-        <v>1.061</v>
+        <v>1.0609999999999999</v>
       </c>
       <c r="T56">
         <v>6426.7</v>
       </c>
       <c r="U56">
-        <v>84.923</v>
+        <v>84.923000000000002</v>
       </c>
       <c r="W56">
         <v>0.151</v>
       </c>
       <c r="X56">
-        <v>0.336</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="Y56">
-        <v>0.589</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>0.58899999999999997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2011</v>
       </c>
@@ -4150,58 +4104,58 @@
         <v>0.151</v>
       </c>
       <c r="F57">
-        <v>0.573</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="G57">
-        <v>0.554</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="H57">
         <v>13102.6</v>
       </c>
       <c r="I57">
-        <v>92.961</v>
+        <v>92.960999999999999</v>
       </c>
       <c r="K57">
         <v>0.159</v>
       </c>
       <c r="L57">
-        <v>0.577</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="M57">
-        <v>0.892</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="N57">
         <v>1888.5</v>
       </c>
       <c r="O57">
-        <v>86.97199999999999</v>
+        <v>86.971999999999994</v>
       </c>
       <c r="Q57">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="R57">
-        <v>0.451</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="S57">
-        <v>0.827</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="T57">
         <v>9134.9</v>
       </c>
       <c r="U57">
-        <v>93.051</v>
+        <v>93.051000000000002</v>
       </c>
       <c r="W57">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="X57">
-        <v>0.632</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="Y57">
         <v>0.371</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2012</v>
       </c>
@@ -4209,16 +4163,16 @@
         <v>25272.2</v>
       </c>
       <c r="C58">
-        <v>87.29000000000001</v>
+        <v>87.29</v>
       </c>
       <c r="E58">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="F58">
-        <v>0.427</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="G58">
-        <v>0.595</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="H58">
         <v>12902.3</v>
@@ -4230,25 +4184,25 @@
         <v>0.128</v>
       </c>
       <c r="L58">
-        <v>0.522</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="M58">
-        <v>0.969</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="N58">
         <v>3707.6</v>
       </c>
       <c r="O58">
-        <v>84.538</v>
+        <v>84.537999999999997</v>
       </c>
       <c r="Q58">
         <v>0.127</v>
       </c>
       <c r="R58">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="T58">
-        <v>8662.299999999999</v>
+        <v>8662.2999999999993</v>
       </c>
       <c r="U58">
         <v>87.503</v>
@@ -4257,69 +4211,69 @@
         <v>0.155</v>
       </c>
       <c r="X58">
-        <v>0.462</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>0.46200000000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2013</v>
       </c>
       <c r="B59">
-        <v>19423.9</v>
+        <v>19423.900000000001</v>
       </c>
       <c r="C59">
-        <v>89.557</v>
+        <v>89.557000000000002</v>
       </c>
       <c r="E59">
         <v>0.13</v>
       </c>
       <c r="F59">
-        <v>0.576</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="G59">
-        <v>0.613</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="H59">
-        <v>8552.200000000001</v>
+        <v>8552.2000000000007</v>
       </c>
       <c r="I59">
-        <v>88.57299999999999</v>
+        <v>88.572999999999993</v>
       </c>
       <c r="K59">
         <v>0.13</v>
       </c>
       <c r="L59">
-        <v>0.469</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="M59">
-        <v>0.893</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="N59">
-        <v>4136.1</v>
+        <v>4136.1000000000004</v>
       </c>
       <c r="O59">
-        <v>88.07899999999999</v>
+        <v>88.078999999999994</v>
       </c>
       <c r="Q59">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="R59">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="T59">
         <v>6735.6</v>
       </c>
       <c r="U59">
-        <v>90.377</v>
+        <v>90.376999999999995</v>
       </c>
       <c r="W59">
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="X59">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2014</v>
       </c>
@@ -4327,37 +4281,37 @@
         <v>13722.7</v>
       </c>
       <c r="C60">
-        <v>86.086</v>
+        <v>86.085999999999999</v>
       </c>
       <c r="E60">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="F60">
         <v>0.32</v>
       </c>
       <c r="G60">
-        <v>0.581</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="H60">
         <v>6677.3</v>
       </c>
       <c r="I60">
-        <v>85.93300000000001</v>
+        <v>85.933000000000007</v>
       </c>
       <c r="K60">
-        <v>0.139</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="L60">
-        <v>0.331</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="M60">
-        <v>0.716</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="N60">
         <v>1646.8</v>
       </c>
       <c r="O60">
-        <v>85.126</v>
+        <v>85.126000000000005</v>
       </c>
       <c r="Q60">
         <v>0.105</v>
@@ -4369,16 +4323,16 @@
         <v>5398.6</v>
       </c>
       <c r="U60">
-        <v>86.642</v>
+        <v>86.641999999999996</v>
       </c>
       <c r="W60">
-        <v>0.147</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="X60">
-        <v>0.382</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>0.38200000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2015</v>
       </c>
@@ -4386,25 +4340,25 @@
         <v>15200.7</v>
       </c>
       <c r="C61">
-        <v>88.517</v>
+        <v>88.516999999999996</v>
       </c>
       <c r="E61">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="F61">
-        <v>0.514</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="G61">
-        <v>0.544</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="H61">
         <v>7160.8</v>
       </c>
       <c r="I61">
-        <v>91.29000000000001</v>
+        <v>91.29</v>
       </c>
       <c r="K61">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="L61">
         <v>0.626</v>
@@ -4416,10 +4370,10 @@
         <v>2326.9</v>
       </c>
       <c r="O61">
-        <v>89.879</v>
+        <v>89.879000000000005</v>
       </c>
       <c r="Q61">
-        <v>0.099</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="R61">
         <v>0.621</v>
@@ -4428,16 +4382,16 @@
         <v>5713</v>
       </c>
       <c r="U61">
-        <v>86.449</v>
+        <v>86.448999999999998</v>
       </c>
       <c r="W61">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="X61">
-        <v>0.403</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>0.40300000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2016</v>
       </c>
@@ -4445,19 +4399,19 @@
         <v>14383.1</v>
       </c>
       <c r="C62">
-        <v>91.17700000000001</v>
+        <v>91.177000000000007</v>
       </c>
       <c r="E62">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F62">
-        <v>0.669</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="G62">
-        <v>0.552</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="H62">
-        <v>8955.299999999999</v>
+        <v>8955.2999999999993</v>
       </c>
       <c r="I62">
         <v>92.759</v>
@@ -4466,7 +4420,7 @@
         <v>0.107</v>
       </c>
       <c r="L62">
-        <v>0.707</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="M62">
         <v>1.143</v>
@@ -4475,28 +4429,28 @@
         <v>1501.9</v>
       </c>
       <c r="O62">
-        <v>92.193</v>
+        <v>92.192999999999998</v>
       </c>
       <c r="Q62">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="R62">
-        <v>0.731</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="T62">
         <v>3925.9</v>
       </c>
       <c r="U62">
-        <v>88.577</v>
+        <v>88.576999999999998</v>
       </c>
       <c r="W62">
         <v>0.113</v>
       </c>
       <c r="X62">
-        <v>0.569</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>0.56899999999999995</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2017</v>
       </c>
@@ -4504,58 +4458,58 @@
         <v>13824.6</v>
       </c>
       <c r="C63">
-        <v>91.538</v>
+        <v>91.537999999999997</v>
       </c>
       <c r="E63">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F63">
-        <v>0.6929999999999999</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="G63">
-        <v>0.631</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="H63">
         <v>9176</v>
       </c>
       <c r="I63">
-        <v>93.254</v>
+        <v>93.254000000000005</v>
       </c>
       <c r="K63">
         <v>0.106</v>
       </c>
       <c r="L63">
-        <v>0.741</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="M63">
-        <v>1.029</v>
+        <v>1.0289999999999999</v>
       </c>
       <c r="N63">
         <v>1743.1</v>
       </c>
       <c r="O63">
-        <v>86.099</v>
+        <v>86.099000000000004</v>
       </c>
       <c r="Q63">
         <v>0.104</v>
       </c>
       <c r="R63">
-        <v>0.319</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="T63">
         <v>2905.5</v>
       </c>
       <c r="U63">
-        <v>93.40000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="W63">
-        <v>0.097</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="X63">
-        <v>0.856</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>0.85599999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2018</v>
       </c>
@@ -4563,28 +4517,28 @@
         <v>17045.5</v>
       </c>
       <c r="C64">
-        <v>92.985</v>
+        <v>92.984999999999999</v>
       </c>
       <c r="E64">
         <v>0.112</v>
       </c>
       <c r="F64">
-        <v>0.711</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="G64">
-        <v>0.803</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="H64">
         <v>9393.6</v>
       </c>
       <c r="I64">
-        <v>96.178</v>
+        <v>96.177999999999997</v>
       </c>
       <c r="K64">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="L64">
-        <v>0.803</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="M64">
         <v>1.284</v>
@@ -4593,25 +4547,25 @@
         <v>3517.8</v>
       </c>
       <c r="O64">
-        <v>89.258</v>
+        <v>89.257999999999996</v>
       </c>
       <c r="Q64">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="R64">
-        <v>0.668</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="T64">
-        <v>4134.1</v>
+        <v>4134.1000000000004</v>
       </c>
       <c r="U64">
-        <v>93.252</v>
+        <v>93.251999999999995</v>
       </c>
       <c r="W64">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="X64">
-        <v>0.6870000000000001</v>
+        <v>0.68700000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/Albacore_SAtl.xlsx
+++ b/Indicator_4/Real_data/Albacore_SAtl.xlsx
@@ -1,300 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770245B2-B7C2-4DC9-B0F0-1E89AF13C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Albacore_SAtl</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>8.559</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.126</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.608</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>147.5</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.758</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.154</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0.503</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.783</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>0.553</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.806</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.129</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.726</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.995</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>0.627</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.605</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.153</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.243</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -428,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -463,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -639,368 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Albacore_SAtl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8.559</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.126</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.608</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.758</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.154</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.503</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.553</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.129</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.726</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.627</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.605</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.153</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.243</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1009,92 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y64"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1956</v>
       </c>
@@ -1102,16 +1067,16 @@
         <v>21</v>
       </c>
       <c r="C2">
-        <v>106.08199999999999</v>
+        <v>106.082</v>
       </c>
       <c r="E2">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2.3420000000000001</v>
+        <v>2.342</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1120,10 +1085,10 @@
         <v>21</v>
       </c>
       <c r="O2">
-        <v>106.08199999999999</v>
+        <v>106.082</v>
       </c>
       <c r="Q2">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1132,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1957</v>
       </c>
@@ -1143,13 +1108,13 @@
         <v>103.456</v>
       </c>
       <c r="E3">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.3969999999999998</v>
+        <v>2.397</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1161,7 +1126,7 @@
         <v>103.456</v>
       </c>
       <c r="Q3">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1170,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>1958</v>
       </c>
@@ -1178,7 +1143,7 @@
         <v>1047</v>
       </c>
       <c r="G4">
-        <v>2.3969999999999998</v>
+        <v>2.397</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1190,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5">
         <v>1959</v>
       </c>
@@ -1198,7 +1163,7 @@
         <v>4715</v>
       </c>
       <c r="G5">
-        <v>2.3969999999999998</v>
+        <v>2.397</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1210,7 +1175,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6">
         <v>1960</v>
       </c>
@@ -1218,16 +1183,16 @@
         <v>10475</v>
       </c>
       <c r="C6">
-        <v>97.917000000000002</v>
+        <v>97.917</v>
       </c>
       <c r="E6">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="F6">
-        <v>0.83299999999999996</v>
+        <v>0.833</v>
       </c>
       <c r="G6">
-        <v>2.3889999999999998</v>
+        <v>2.389</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1236,19 +1201,19 @@
         <v>8673</v>
       </c>
       <c r="O6">
-        <v>97.917000000000002</v>
+        <v>97.917</v>
       </c>
       <c r="Q6">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="R6">
-        <v>0.83299999999999996</v>
+        <v>0.833</v>
       </c>
       <c r="T6">
         <v>1802</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>1961</v>
       </c>
@@ -1256,7 +1221,7 @@
         <v>10765</v>
       </c>
       <c r="G7">
-        <v>2.3780000000000001</v>
+        <v>2.378</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1268,7 +1233,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>1962</v>
       </c>
@@ -1282,10 +1247,10 @@
         <v>0.1</v>
       </c>
       <c r="F8">
-        <v>0.88900000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="G8">
-        <v>2.3290000000000002</v>
+        <v>2.329</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1300,13 +1265,13 @@
         <v>0.1</v>
       </c>
       <c r="R8">
-        <v>0.88900000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="T8">
         <v>2549</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>1963</v>
       </c>
@@ -1314,16 +1279,16 @@
         <v>17385</v>
       </c>
       <c r="C9">
-        <v>101.20699999999999</v>
+        <v>101.207</v>
       </c>
       <c r="E9">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="F9">
-        <v>0.96599999999999997</v>
+        <v>0.966</v>
       </c>
       <c r="G9">
-        <v>2.2200000000000002</v>
+        <v>2.22</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1332,19 +1297,19 @@
         <v>15104</v>
       </c>
       <c r="O9">
-        <v>101.20699999999999</v>
+        <v>101.207</v>
       </c>
       <c r="Q9">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="R9">
-        <v>0.96599999999999997</v>
+        <v>0.966</v>
       </c>
       <c r="T9">
         <v>2281</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>1964</v>
       </c>
@@ -1352,16 +1317,16 @@
         <v>25999</v>
       </c>
       <c r="C10">
-        <v>96.849000000000004</v>
+        <v>96.849</v>
       </c>
       <c r="E10">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="F10">
-        <v>0.80800000000000005</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G10">
-        <v>2.1190000000000002</v>
+        <v>2.119</v>
       </c>
       <c r="H10">
         <v>115</v>
@@ -1370,19 +1335,19 @@
         <v>23738</v>
       </c>
       <c r="O10">
-        <v>96.849000000000004</v>
+        <v>96.849</v>
       </c>
       <c r="Q10">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="R10">
-        <v>0.80800000000000005</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="T10">
         <v>2146</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11">
         <v>1965</v>
       </c>
@@ -1393,13 +1358,13 @@
         <v>86.63</v>
       </c>
       <c r="E11">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="F11">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="G11">
-        <v>1.9470000000000001</v>
+        <v>1.947</v>
       </c>
       <c r="H11">
         <v>346</v>
@@ -1411,16 +1376,16 @@
         <v>86.63</v>
       </c>
       <c r="Q11">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="R11">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="T11">
         <v>1190</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>1966</v>
       </c>
@@ -1428,16 +1393,16 @@
         <v>27296</v>
       </c>
       <c r="C12">
-        <v>87.135000000000005</v>
+        <v>87.13500000000001</v>
       </c>
       <c r="E12">
         <v>0.12</v>
       </c>
       <c r="F12">
-        <v>0.41199999999999998</v>
+        <v>0.412</v>
       </c>
       <c r="G12">
-        <v>1.8169999999999999</v>
+        <v>1.817</v>
       </c>
       <c r="H12">
         <v>5275</v>
@@ -1446,19 +1411,19 @@
         <v>21023</v>
       </c>
       <c r="O12">
-        <v>87.135000000000005</v>
+        <v>87.13500000000001</v>
       </c>
       <c r="Q12">
         <v>0.12</v>
       </c>
       <c r="R12">
-        <v>0.41199999999999998</v>
+        <v>0.412</v>
       </c>
       <c r="T12">
         <v>998</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13">
         <v>1967</v>
       </c>
@@ -1466,10 +1431,10 @@
         <v>15883</v>
       </c>
       <c r="C13">
-        <v>86.786000000000001</v>
+        <v>86.786</v>
       </c>
       <c r="E13">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="F13">
         <v>0.5</v>
@@ -1481,16 +1446,16 @@
         <v>7412</v>
       </c>
       <c r="M13">
-        <v>2.5230000000000001</v>
+        <v>2.523</v>
       </c>
       <c r="N13">
         <v>7719</v>
       </c>
       <c r="O13">
-        <v>86.786000000000001</v>
+        <v>86.786</v>
       </c>
       <c r="Q13">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="R13">
         <v>0.5</v>
@@ -1499,7 +1464,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>1968</v>
       </c>
@@ -1507,7 +1472,7 @@
         <v>25688</v>
       </c>
       <c r="C14">
-        <v>83.984999999999999</v>
+        <v>83.985</v>
       </c>
       <c r="E14">
         <v>0.121</v>
@@ -1516,7 +1481,7 @@
         <v>0.252</v>
       </c>
       <c r="G14">
-        <v>1.4490000000000001</v>
+        <v>1.449</v>
       </c>
       <c r="H14">
         <v>12489</v>
@@ -1528,7 +1493,7 @@
         <v>11857</v>
       </c>
       <c r="O14">
-        <v>83.984999999999999</v>
+        <v>83.985</v>
       </c>
       <c r="Q14">
         <v>0.121</v>
@@ -1540,7 +1505,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15">
         <v>1969</v>
       </c>
@@ -1554,10 +1519,10 @@
         <v>0.19</v>
       </c>
       <c r="F15">
-        <v>0.64600000000000002</v>
+        <v>0.646</v>
       </c>
       <c r="G15">
-        <v>1.3480000000000001</v>
+        <v>1.348</v>
       </c>
       <c r="H15">
         <v>21732</v>
@@ -1569,28 +1534,28 @@
         <v>6331</v>
       </c>
       <c r="O15">
-        <v>88.843000000000004</v>
+        <v>88.843</v>
       </c>
       <c r="Q15">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="R15">
-        <v>0.60099999999999998</v>
+        <v>0.601</v>
       </c>
       <c r="T15">
         <v>430</v>
       </c>
       <c r="U15">
-        <v>88.382000000000005</v>
+        <v>88.38200000000001</v>
       </c>
       <c r="W15">
-        <v>0.26100000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="X15">
-        <v>0.69099999999999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6909999999999999</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1970</v>
       </c>
@@ -1598,16 +1563,16 @@
         <v>23653</v>
       </c>
       <c r="C16">
-        <v>83.775000000000006</v>
+        <v>83.77500000000001</v>
       </c>
       <c r="E16">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="F16">
         <v>0.496</v>
       </c>
       <c r="G16">
-        <v>1.3759999999999999</v>
+        <v>1.376</v>
       </c>
       <c r="H16">
         <v>17255</v>
@@ -1619,28 +1584,28 @@
         <v>5898</v>
       </c>
       <c r="O16">
-        <v>82.935000000000002</v>
+        <v>82.935</v>
       </c>
       <c r="Q16">
         <v>0.153</v>
       </c>
       <c r="R16">
-        <v>0.32600000000000001</v>
+        <v>0.326</v>
       </c>
       <c r="T16">
         <v>500</v>
       </c>
       <c r="U16">
-        <v>84.614999999999995</v>
+        <v>84.61499999999999</v>
       </c>
       <c r="W16">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="X16">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1971</v>
       </c>
@@ -1648,16 +1613,16 @@
         <v>24885</v>
       </c>
       <c r="C17">
-        <v>93.850999999999999</v>
+        <v>93.851</v>
       </c>
       <c r="E17">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F17">
-        <v>0.83799999999999997</v>
+        <v>0.838</v>
       </c>
       <c r="G17">
-        <v>1.3149999999999999</v>
+        <v>1.315</v>
       </c>
       <c r="H17">
         <v>21323</v>
@@ -1672,16 +1637,16 @@
         <v>344</v>
       </c>
       <c r="U17">
-        <v>93.850999999999999</v>
+        <v>93.851</v>
       </c>
       <c r="W17">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X17">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.838</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1972</v>
       </c>
@@ -1689,16 +1654,16 @@
         <v>33189</v>
       </c>
       <c r="C18">
-        <v>97.707999999999998</v>
+        <v>97.708</v>
       </c>
       <c r="E18">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="F18">
-        <v>0.95799999999999996</v>
+        <v>0.958</v>
       </c>
       <c r="G18">
-        <v>1.2150000000000001</v>
+        <v>1.215</v>
       </c>
       <c r="H18">
         <v>30640</v>
@@ -1713,16 +1678,16 @@
         <v>462</v>
       </c>
       <c r="U18">
-        <v>97.707999999999998</v>
+        <v>97.708</v>
       </c>
       <c r="W18">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="X18">
-        <v>0.95799999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.958</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1973</v>
       </c>
@@ -1730,13 +1695,13 @@
         <v>28234.1</v>
       </c>
       <c r="C19">
-        <v>93.097999999999999</v>
+        <v>93.098</v>
       </c>
       <c r="E19">
         <v>0.1</v>
       </c>
       <c r="F19">
-        <v>0.72799999999999998</v>
+        <v>0.728</v>
       </c>
       <c r="G19">
         <v>1.147</v>
@@ -1745,16 +1710,16 @@
         <v>25888</v>
       </c>
       <c r="M19">
-        <v>0.97899999999999998</v>
+        <v>0.979</v>
       </c>
       <c r="N19">
         <v>277</v>
       </c>
       <c r="O19">
-        <v>87.972999999999999</v>
+        <v>87.973</v>
       </c>
       <c r="Q19">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="R19">
         <v>0.5</v>
@@ -1763,16 +1728,16 @@
         <v>2069.1</v>
       </c>
       <c r="U19">
-        <v>98.221999999999994</v>
+        <v>98.22199999999999</v>
       </c>
       <c r="W19">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="X19">
-        <v>0.95599999999999996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.956</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1974</v>
       </c>
@@ -1783,10 +1748,10 @@
         <v>94.369</v>
       </c>
       <c r="E20">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="F20">
-        <v>0.83099999999999996</v>
+        <v>0.831</v>
       </c>
       <c r="G20">
         <v>1.06</v>
@@ -1795,34 +1760,34 @@
         <v>19079</v>
       </c>
       <c r="M20">
-        <v>1.0129999999999999</v>
+        <v>1.013</v>
       </c>
       <c r="N20">
         <v>109</v>
       </c>
       <c r="O20">
-        <v>91.667000000000002</v>
+        <v>91.667</v>
       </c>
       <c r="Q20">
         <v>0.1</v>
       </c>
       <c r="R20">
-        <v>0.73299999999999998</v>
+        <v>0.733</v>
       </c>
       <c r="T20">
         <v>528</v>
       </c>
       <c r="U20">
-        <v>97.072000000000003</v>
+        <v>97.072</v>
       </c>
       <c r="W20">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="X20">
-        <v>0.92800000000000005</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.928</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1975</v>
       </c>
@@ -1830,28 +1795,28 @@
         <v>17607</v>
       </c>
       <c r="C21">
-        <v>90.989000000000004</v>
+        <v>90.989</v>
       </c>
       <c r="E21">
         <v>0.12</v>
       </c>
       <c r="F21">
-        <v>0.63100000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="G21">
-        <v>0.90300000000000002</v>
+        <v>0.903</v>
       </c>
       <c r="H21">
         <v>16614</v>
       </c>
       <c r="I21">
-        <v>85.161000000000001</v>
+        <v>85.161</v>
       </c>
       <c r="K21">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="L21">
-        <v>0.34399999999999997</v>
+        <v>0.344</v>
       </c>
       <c r="M21">
         <v>1.18</v>
@@ -1860,7 +1825,7 @@
         <v>306</v>
       </c>
       <c r="O21">
-        <v>91.037999999999997</v>
+        <v>91.038</v>
       </c>
       <c r="Q21">
         <v>0.152</v>
@@ -1872,16 +1837,16 @@
         <v>687</v>
       </c>
       <c r="U21">
-        <v>96.768000000000001</v>
+        <v>96.768</v>
       </c>
       <c r="W21">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="X21">
-        <v>0.93899999999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.9389999999999999</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1976</v>
       </c>
@@ -1889,31 +1854,31 @@
         <v>19375</v>
       </c>
       <c r="C22">
-        <v>94.007000000000005</v>
+        <v>94.00700000000001</v>
       </c>
       <c r="E22">
-        <v>0.11700000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="F22">
-        <v>0.72899999999999998</v>
+        <v>0.729</v>
       </c>
       <c r="G22">
-        <v>0.81699999999999995</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H22">
         <v>17976</v>
       </c>
       <c r="I22">
-        <v>85.653000000000006</v>
+        <v>85.65300000000001</v>
       </c>
       <c r="K22">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="L22">
         <v>0.41</v>
       </c>
       <c r="M22">
-        <v>1.0469999999999999</v>
+        <v>1.047</v>
       </c>
       <c r="N22">
         <v>73</v>
@@ -1922,7 +1887,7 @@
         <v>102.45</v>
       </c>
       <c r="Q22">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="R22">
         <v>0.91</v>
@@ -1934,16 +1899,16 @@
         <v>1326</v>
       </c>
       <c r="U22">
-        <v>93.918000000000006</v>
+        <v>93.91800000000001</v>
       </c>
       <c r="W22">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X22">
-        <v>0.86499999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>1977</v>
       </c>
@@ -1951,28 +1916,28 @@
         <v>21455</v>
       </c>
       <c r="C23">
-        <v>89.055999999999997</v>
+        <v>89.056</v>
       </c>
       <c r="E23">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="F23">
-        <v>0.56200000000000006</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G23">
-        <v>0.82199999999999995</v>
+        <v>0.822</v>
       </c>
       <c r="H23">
         <v>19858</v>
       </c>
       <c r="I23">
-        <v>83.570999999999998</v>
+        <v>83.571</v>
       </c>
       <c r="K23">
         <v>0.156</v>
       </c>
       <c r="L23">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="M23">
         <v>1.222</v>
@@ -1981,22 +1946,22 @@
         <v>105</v>
       </c>
       <c r="O23">
-        <v>94.540999999999997</v>
+        <v>94.541</v>
       </c>
       <c r="Q23">
         <v>0.125</v>
       </c>
       <c r="R23">
-        <v>0.77100000000000002</v>
+        <v>0.771</v>
       </c>
       <c r="S23">
-        <v>0.77500000000000002</v>
+        <v>0.775</v>
       </c>
       <c r="T23">
         <v>1492</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24">
         <v>1978</v>
       </c>
@@ -2004,43 +1969,43 @@
         <v>23095</v>
       </c>
       <c r="C24">
-        <v>89.828000000000003</v>
+        <v>89.828</v>
       </c>
       <c r="E24">
-        <v>0.13600000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="F24">
         <v>0.625</v>
       </c>
       <c r="G24">
-        <v>0.84499999999999997</v>
+        <v>0.845</v>
       </c>
       <c r="H24">
         <v>21837</v>
       </c>
       <c r="I24">
-        <v>84.638000000000005</v>
+        <v>84.63800000000001</v>
       </c>
       <c r="K24">
-        <v>0.17399999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="L24">
-        <v>0.42099999999999999</v>
+        <v>0.421</v>
       </c>
       <c r="M24">
-        <v>1.1120000000000001</v>
+        <v>1.112</v>
       </c>
       <c r="N24">
         <v>135</v>
       </c>
       <c r="O24">
-        <v>90.397000000000006</v>
+        <v>90.39700000000001</v>
       </c>
       <c r="Q24">
         <v>0.154</v>
       </c>
       <c r="R24">
-        <v>0.60299999999999998</v>
+        <v>0.603</v>
       </c>
       <c r="S24">
         <v>1.446</v>
@@ -2049,16 +2014,16 @@
         <v>1123</v>
       </c>
       <c r="U24">
-        <v>94.447999999999993</v>
+        <v>94.44799999999999</v>
       </c>
       <c r="W24">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="X24">
-        <v>0.85099999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.851</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1979</v>
       </c>
@@ -2066,13 +2031,13 @@
         <v>22640</v>
       </c>
       <c r="C25">
-        <v>90.105000000000004</v>
+        <v>90.105</v>
       </c>
       <c r="E25">
         <v>0.127</v>
       </c>
       <c r="F25">
-        <v>0.61299999999999999</v>
+        <v>0.613</v>
       </c>
       <c r="G25">
         <v>0.85</v>
@@ -2084,28 +2049,28 @@
         <v>86.73</v>
       </c>
       <c r="K25">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="L25">
         <v>0.439</v>
       </c>
       <c r="M25">
-        <v>1.1080000000000001</v>
+        <v>1.108</v>
       </c>
       <c r="N25">
         <v>105</v>
       </c>
       <c r="O25">
-        <v>86.923000000000002</v>
+        <v>86.923</v>
       </c>
       <c r="Q25">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="R25">
         <v>0.5</v>
       </c>
       <c r="S25">
-        <v>0.58399999999999996</v>
+        <v>0.584</v>
       </c>
       <c r="T25">
         <v>1317</v>
@@ -2114,13 +2079,13 @@
         <v>96.66</v>
       </c>
       <c r="W25">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="X25">
-        <v>0.90100000000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.901</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1980</v>
       </c>
@@ -2131,19 +2096,19 @@
         <v>91.872</v>
       </c>
       <c r="E26">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="F26">
-        <v>0.64100000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="G26">
-        <v>0.84399999999999997</v>
+        <v>0.844</v>
       </c>
       <c r="H26">
         <v>19400</v>
       </c>
       <c r="I26">
-        <v>81.225999999999999</v>
+        <v>81.226</v>
       </c>
       <c r="K26">
         <v>0.193</v>
@@ -2152,19 +2117,19 @@
         <v>0.315</v>
       </c>
       <c r="M26">
-        <v>1.1359999999999999</v>
+        <v>1.136</v>
       </c>
       <c r="N26">
         <v>333</v>
       </c>
       <c r="O26">
-        <v>90.090999999999994</v>
+        <v>90.09099999999999</v>
       </c>
       <c r="Q26">
         <v>0.152</v>
       </c>
       <c r="R26">
-        <v>0.56399999999999995</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="S26">
         <v>0.871</v>
@@ -2173,16 +2138,16 @@
         <v>3213</v>
       </c>
       <c r="U26">
-        <v>98.085999999999999</v>
+        <v>98.086</v>
       </c>
       <c r="W26">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="X26">
-        <v>0.84299999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.843</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1981</v>
       </c>
@@ -2190,31 +2155,31 @@
         <v>24040</v>
       </c>
       <c r="C27">
-        <v>95.765000000000001</v>
+        <v>95.765</v>
       </c>
       <c r="E27">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="F27">
-        <v>0.75600000000000001</v>
+        <v>0.756</v>
       </c>
       <c r="G27">
-        <v>0.83299999999999996</v>
+        <v>0.833</v>
       </c>
       <c r="H27">
         <v>18869</v>
       </c>
       <c r="I27">
-        <v>89.546999999999997</v>
+        <v>89.547</v>
       </c>
       <c r="K27">
         <v>0.189</v>
       </c>
       <c r="L27">
-        <v>0.57699999999999996</v>
+        <v>0.577</v>
       </c>
       <c r="M27">
-        <v>1.0069999999999999</v>
+        <v>1.007</v>
       </c>
       <c r="N27">
         <v>558</v>
@@ -2223,10 +2188,10 @@
         <v>91.36</v>
       </c>
       <c r="Q27">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="R27">
-        <v>0.56100000000000005</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="S27">
         <v>1.853</v>
@@ -2238,13 +2203,13 @@
         <v>101.077</v>
       </c>
       <c r="W27">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="X27">
-        <v>0.94199999999999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.9419999999999999</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>1982</v>
       </c>
@@ -2255,43 +2220,43 @@
         <v>93.637</v>
       </c>
       <c r="E28">
-        <v>0.16800000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="F28">
-        <v>0.63900000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="G28">
-        <v>0.82799999999999996</v>
+        <v>0.828</v>
       </c>
       <c r="H28">
         <v>23363</v>
       </c>
       <c r="I28">
-        <v>86.194000000000003</v>
+        <v>86.194</v>
       </c>
       <c r="K28">
         <v>0.17</v>
       </c>
       <c r="L28">
-        <v>0.42199999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="M28">
-        <v>0.98399999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="N28">
         <v>569</v>
       </c>
       <c r="O28">
-        <v>87.921999999999997</v>
+        <v>87.922</v>
       </c>
       <c r="Q28">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="R28">
-        <v>0.50600000000000001</v>
+        <v>0.506</v>
       </c>
       <c r="S28">
-        <v>1.4359999999999999</v>
+        <v>1.436</v>
       </c>
       <c r="T28">
         <v>5740</v>
@@ -2300,13 +2265,13 @@
         <v>100.217</v>
       </c>
       <c r="W28">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="X28">
-        <v>0.81299999999999994</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.8129999999999999</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1983</v>
       </c>
@@ -2314,7 +2279,7 @@
         <v>14918</v>
       </c>
       <c r="C29">
-        <v>97.344999999999999</v>
+        <v>97.345</v>
       </c>
       <c r="E29">
         <v>0.108</v>
@@ -2323,37 +2288,37 @@
         <v>0.82</v>
       </c>
       <c r="G29">
-        <v>0.81899999999999995</v>
+        <v>0.819</v>
       </c>
       <c r="H29">
         <v>10101</v>
       </c>
       <c r="I29">
-        <v>88.043000000000006</v>
+        <v>88.04300000000001</v>
       </c>
       <c r="K29">
         <v>0.189</v>
       </c>
       <c r="L29">
-        <v>0.47899999999999998</v>
+        <v>0.479</v>
       </c>
       <c r="M29">
-        <v>0.94299999999999995</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N29">
         <v>162</v>
       </c>
       <c r="O29">
-        <v>97.707999999999998</v>
+        <v>97.708</v>
       </c>
       <c r="Q29">
         <v>0.113</v>
       </c>
       <c r="R29">
-        <v>0.83299999999999996</v>
+        <v>0.833</v>
       </c>
       <c r="S29">
-        <v>1.1679999999999999</v>
+        <v>1.168</v>
       </c>
       <c r="T29">
         <v>4655</v>
@@ -2362,16 +2327,16 @@
         <v>100.324</v>
       </c>
       <c r="W29">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="X29">
-        <v>0.92900000000000005</v>
+        <v>0.929</v>
       </c>
       <c r="Y29">
-        <v>1.6890000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.689</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>1984</v>
       </c>
@@ -2379,13 +2344,13 @@
         <v>14599</v>
       </c>
       <c r="C30">
-        <v>96.951999999999998</v>
+        <v>96.952</v>
       </c>
       <c r="E30">
         <v>0.115</v>
       </c>
       <c r="F30">
-        <v>0.81399999999999995</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G30">
         <v>0.79</v>
@@ -2394,16 +2359,16 @@
         <v>8237</v>
       </c>
       <c r="I30">
-        <v>94.608999999999995</v>
+        <v>94.60899999999999</v>
       </c>
       <c r="K30">
         <v>0.19</v>
       </c>
       <c r="L30">
-        <v>0.60499999999999998</v>
+        <v>0.605</v>
       </c>
       <c r="M30">
-        <v>1.0840000000000001</v>
+        <v>1.084</v>
       </c>
       <c r="N30">
         <v>224</v>
@@ -2415,7 +2380,7 @@
         <v>0.114</v>
       </c>
       <c r="R30">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S30">
         <v>1.169</v>
@@ -2424,19 +2389,19 @@
         <v>6138</v>
       </c>
       <c r="U30">
-        <v>97.986999999999995</v>
+        <v>97.98699999999999</v>
       </c>
       <c r="W30">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="X30">
-        <v>0.88500000000000001</v>
+        <v>0.885</v>
       </c>
       <c r="Y30">
-        <v>1.4590000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.459</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>1985</v>
       </c>
@@ -2450,49 +2415,49 @@
         <v>0.155</v>
       </c>
       <c r="F31">
-        <v>0.46600000000000003</v>
+        <v>0.466</v>
       </c>
       <c r="G31">
-        <v>0.70199999999999996</v>
+        <v>0.702</v>
       </c>
       <c r="H31">
         <v>20154</v>
       </c>
       <c r="I31">
-        <v>83.222999999999999</v>
+        <v>83.223</v>
       </c>
       <c r="K31">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="L31">
-        <v>0.36099999999999999</v>
+        <v>0.361</v>
       </c>
       <c r="M31">
-        <v>0.98899999999999999</v>
+        <v>0.989</v>
       </c>
       <c r="N31">
         <v>623</v>
       </c>
       <c r="O31">
-        <v>91.350999999999999</v>
+        <v>91.351</v>
       </c>
       <c r="Q31">
-        <v>0.17899999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="R31">
-        <v>0.64900000000000002</v>
+        <v>0.649</v>
       </c>
       <c r="S31">
         <v>2.032</v>
       </c>
       <c r="T31">
-        <v>10320.299999999999</v>
+        <v>10320.3</v>
       </c>
       <c r="U31">
-        <v>86.203999999999994</v>
+        <v>86.20399999999999</v>
       </c>
       <c r="W31">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="X31">
         <v>0.44</v>
@@ -2501,7 +2466,7 @@
         <v>1.526</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32">
         <v>1986</v>
       </c>
@@ -2509,13 +2474,13 @@
         <v>37288</v>
       </c>
       <c r="C32">
-        <v>90.203000000000003</v>
+        <v>90.203</v>
       </c>
       <c r="E32">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="F32">
-        <v>0.58899999999999997</v>
+        <v>0.589</v>
       </c>
       <c r="G32">
         <v>0.746</v>
@@ -2524,49 +2489,49 @@
         <v>27913</v>
       </c>
       <c r="I32">
-        <v>85.019000000000005</v>
+        <v>85.01900000000001</v>
       </c>
       <c r="K32">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="L32">
-        <v>0.40200000000000002</v>
+        <v>0.402</v>
       </c>
       <c r="M32">
-        <v>0.98399999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="N32">
         <v>739</v>
       </c>
       <c r="O32">
-        <v>97.143000000000001</v>
+        <v>97.143</v>
       </c>
       <c r="Q32">
         <v>0.104</v>
       </c>
       <c r="R32">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S32">
-        <v>2.5030000000000001</v>
+        <v>2.503</v>
       </c>
       <c r="T32">
         <v>8636</v>
       </c>
       <c r="U32">
-        <v>89.617000000000004</v>
+        <v>89.617</v>
       </c>
       <c r="W32">
-        <v>0.13600000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="X32">
-        <v>0.57699999999999996</v>
+        <v>0.577</v>
       </c>
       <c r="Y32">
-        <v>1.5089999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.509</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>1987</v>
       </c>
@@ -2574,55 +2539,55 @@
         <v>40630</v>
       </c>
       <c r="C33">
-        <v>89.65</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="E33">
         <v>0.109</v>
       </c>
       <c r="F33">
-        <v>0.56200000000000006</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G33">
-        <v>0.80800000000000005</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H33">
         <v>29173</v>
       </c>
       <c r="I33">
-        <v>83.667000000000002</v>
+        <v>83.667</v>
       </c>
       <c r="K33">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="L33">
-        <v>0.36299999999999999</v>
+        <v>0.363</v>
       </c>
       <c r="M33">
-        <v>0.82199999999999995</v>
+        <v>0.822</v>
       </c>
       <c r="N33">
         <v>357</v>
       </c>
       <c r="O33">
-        <v>99.167000000000002</v>
+        <v>99.167</v>
       </c>
       <c r="Q33">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="R33">
-        <v>0.94399999999999995</v>
+        <v>0.944</v>
       </c>
       <c r="S33">
-        <v>0.98199999999999998</v>
+        <v>0.982</v>
       </c>
       <c r="T33">
         <v>11100</v>
       </c>
       <c r="U33">
-        <v>88.472999999999999</v>
+        <v>88.473</v>
       </c>
       <c r="W33">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="X33">
         <v>0.501</v>
@@ -2631,7 +2596,7 @@
         <v>1.411</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>1988</v>
       </c>
@@ -2639,81 +2604,81 @@
         <v>30173</v>
       </c>
       <c r="C34">
-        <v>88.876999999999995</v>
+        <v>88.877</v>
       </c>
       <c r="E34">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="F34">
         <v>0.51</v>
       </c>
       <c r="G34">
-        <v>0.74099999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="H34">
         <v>20926</v>
       </c>
       <c r="I34">
-        <v>89.599000000000004</v>
+        <v>89.599</v>
       </c>
       <c r="K34">
         <v>0.152</v>
       </c>
       <c r="L34">
-        <v>0.48599999999999999</v>
+        <v>0.486</v>
       </c>
       <c r="M34">
-        <v>0.66300000000000003</v>
+        <v>0.663</v>
       </c>
       <c r="N34">
         <v>405</v>
       </c>
       <c r="O34">
-        <v>96.841999999999999</v>
+        <v>96.842</v>
       </c>
       <c r="Q34">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="R34">
-        <v>0.73699999999999999</v>
+        <v>0.737</v>
       </c>
       <c r="S34">
-        <v>0.68899999999999995</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="T34">
         <v>8842</v>
       </c>
       <c r="U34">
-        <v>85.980999999999995</v>
+        <v>85.98099999999999</v>
       </c>
       <c r="W34">
-        <v>0.13200000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="X34">
         <v>0.443</v>
       </c>
       <c r="Y34">
-        <v>1.4670000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.467</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>1989</v>
       </c>
       <c r="B35">
-        <v>27211.599999999999</v>
+        <v>27211.6</v>
       </c>
       <c r="C35">
-        <v>89.153000000000006</v>
+        <v>89.15300000000001</v>
       </c>
       <c r="E35">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="F35">
-        <v>0.52200000000000002</v>
+        <v>0.522</v>
       </c>
       <c r="G35">
-        <v>0.64300000000000002</v>
+        <v>0.643</v>
       </c>
       <c r="H35">
         <v>18440</v>
@@ -2722,28 +2687,28 @@
         <v>88.52</v>
       </c>
       <c r="K35">
-        <v>0.13900000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="L35">
-        <v>0.54100000000000004</v>
+        <v>0.541</v>
       </c>
       <c r="M35">
-        <v>0.57599999999999996</v>
+        <v>0.576</v>
       </c>
       <c r="N35">
         <v>450</v>
       </c>
       <c r="O35">
-        <v>97.308000000000007</v>
+        <v>97.30800000000001</v>
       </c>
       <c r="Q35">
         <v>0.122</v>
       </c>
       <c r="R35">
-        <v>0.80800000000000005</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="S35">
-        <v>0.85899999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="T35">
         <v>8321.6</v>
@@ -2761,7 +2726,7 @@
         <v>1.754</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36">
         <v>1990</v>
       </c>
@@ -2769,22 +2734,22 @@
         <v>28714</v>
       </c>
       <c r="C36">
-        <v>88.048000000000002</v>
+        <v>88.048</v>
       </c>
       <c r="E36">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="F36">
-        <v>0.48499999999999999</v>
+        <v>0.485</v>
       </c>
       <c r="G36">
-        <v>0.53500000000000003</v>
+        <v>0.535</v>
       </c>
       <c r="H36">
         <v>20461</v>
       </c>
       <c r="I36">
-        <v>85.194999999999993</v>
+        <v>85.19499999999999</v>
       </c>
       <c r="K36">
         <v>0.122</v>
@@ -2793,19 +2758,19 @@
         <v>0.43</v>
       </c>
       <c r="M36">
-        <v>0.58599999999999997</v>
+        <v>0.586</v>
       </c>
       <c r="N36">
         <v>587</v>
       </c>
       <c r="O36">
-        <v>97.608999999999995</v>
+        <v>97.60899999999999</v>
       </c>
       <c r="Q36">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="R36">
-        <v>0.78300000000000003</v>
+        <v>0.783</v>
       </c>
       <c r="S36">
         <v>1.175</v>
@@ -2814,19 +2779,19 @@
         <v>7666</v>
       </c>
       <c r="U36">
-        <v>81.340999999999994</v>
+        <v>81.34099999999999</v>
       </c>
       <c r="W36">
         <v>0.193</v>
       </c>
       <c r="X36">
-        <v>0.24399999999999999</v>
+        <v>0.244</v>
       </c>
       <c r="Y36">
-        <v>1.1479999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.148</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>1991</v>
       </c>
@@ -2840,37 +2805,37 @@
         <v>0.129</v>
       </c>
       <c r="F37">
-        <v>0.35899999999999999</v>
+        <v>0.359</v>
       </c>
       <c r="G37">
-        <v>0.50700000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="H37">
         <v>19914</v>
       </c>
       <c r="I37">
-        <v>74.838999999999999</v>
+        <v>74.839</v>
       </c>
       <c r="K37">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0.63300000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="N37">
         <v>804.4</v>
       </c>
       <c r="O37">
-        <v>96.667000000000002</v>
+        <v>96.667</v>
       </c>
       <c r="Q37">
         <v>0.106</v>
       </c>
       <c r="R37">
-        <v>0.85199999999999998</v>
+        <v>0.852</v>
       </c>
       <c r="S37">
         <v>1.343</v>
@@ -2879,19 +2844,19 @@
         <v>5297.7</v>
       </c>
       <c r="U37">
-        <v>83.870999999999995</v>
+        <v>83.871</v>
       </c>
       <c r="W37">
-        <v>0.21199999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="X37">
-        <v>0.22600000000000001</v>
+        <v>0.226</v>
       </c>
       <c r="Y37">
         <v>1.333</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38">
         <v>1992</v>
       </c>
@@ -2899,7 +2864,7 @@
         <v>36564</v>
       </c>
       <c r="C38">
-        <v>92.495999999999995</v>
+        <v>92.496</v>
       </c>
       <c r="E38">
         <v>0.13</v>
@@ -2914,22 +2879,22 @@
         <v>23068</v>
       </c>
       <c r="I38">
-        <v>89.662999999999997</v>
+        <v>89.663</v>
       </c>
       <c r="K38">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="L38">
-        <v>0.52300000000000002</v>
+        <v>0.523</v>
       </c>
       <c r="M38">
-        <v>0.72699999999999998</v>
+        <v>0.727</v>
       </c>
       <c r="N38">
         <v>1000.9</v>
       </c>
       <c r="O38">
-        <v>90.429000000000002</v>
+        <v>90.429</v>
       </c>
       <c r="Q38">
         <v>0.154</v>
@@ -2938,57 +2903,57 @@
         <v>0.6</v>
       </c>
       <c r="S38">
-        <v>0.72699999999999998</v>
+        <v>0.727</v>
       </c>
       <c r="T38">
         <v>12495.1</v>
       </c>
       <c r="U38">
-        <v>94.944999999999993</v>
+        <v>94.94499999999999</v>
       </c>
       <c r="W38">
         <v>0.113</v>
       </c>
       <c r="X38">
-        <v>0.68899999999999995</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="Y38">
-        <v>0.88400000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.884</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>1993</v>
       </c>
       <c r="B39">
-        <v>32814.300000000003</v>
+        <v>32814.3</v>
       </c>
       <c r="C39">
-        <v>88.801000000000002</v>
+        <v>88.801</v>
       </c>
       <c r="E39">
-        <v>0.13900000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="F39">
-        <v>0.53100000000000003</v>
+        <v>0.531</v>
       </c>
       <c r="G39">
-        <v>0.53800000000000003</v>
+        <v>0.538</v>
       </c>
       <c r="H39">
         <v>19420</v>
       </c>
       <c r="I39">
-        <v>84.224000000000004</v>
+        <v>84.224</v>
       </c>
       <c r="K39">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="L39">
-        <v>0.40400000000000003</v>
+        <v>0.404</v>
       </c>
       <c r="M39">
-        <v>0.76900000000000002</v>
+        <v>0.769</v>
       </c>
       <c r="N39">
         <v>748.5</v>
@@ -2997,10 +2962,10 @@
         <v>88.69</v>
       </c>
       <c r="Q39">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="R39">
-        <v>0.57099999999999995</v>
+        <v>0.571</v>
       </c>
       <c r="S39">
         <v>0.62</v>
@@ -3009,19 +2974,19 @@
         <v>12645.8</v>
       </c>
       <c r="U39">
-        <v>91.144999999999996</v>
+        <v>91.145</v>
       </c>
       <c r="W39">
         <v>0.124</v>
       </c>
       <c r="X39">
-        <v>0.57499999999999996</v>
+        <v>0.575</v>
       </c>
       <c r="Y39">
         <v>1.546</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40">
         <v>1994</v>
       </c>
@@ -3035,10 +3000,10 @@
         <v>0.15</v>
       </c>
       <c r="F40">
-        <v>0.49199999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="G40">
-        <v>0.57499999999999996</v>
+        <v>0.575</v>
       </c>
       <c r="H40">
         <v>22575.8</v>
@@ -3047,7 +3012,7 @@
         <v>83.88</v>
       </c>
       <c r="K40">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="L40">
         <v>0.443</v>
@@ -3068,13 +3033,13 @@
         <v>0.52</v>
       </c>
       <c r="S40">
-        <v>0.84599999999999997</v>
+        <v>0.846</v>
       </c>
       <c r="T40">
         <v>11801.2</v>
       </c>
       <c r="U40">
-        <v>88.058999999999997</v>
+        <v>88.059</v>
       </c>
       <c r="W40">
         <v>0.122</v>
@@ -3083,36 +3048,36 @@
         <v>0.502</v>
       </c>
       <c r="Y40">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>1995</v>
       </c>
       <c r="B41">
-        <v>27553.599999999999</v>
+        <v>27553.6</v>
       </c>
       <c r="C41">
-        <v>85.120999999999995</v>
+        <v>85.121</v>
       </c>
       <c r="E41">
-        <v>0.16900000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="F41">
-        <v>0.39900000000000002</v>
+        <v>0.399</v>
       </c>
       <c r="G41">
-        <v>0.53300000000000003</v>
+        <v>0.533</v>
       </c>
       <c r="H41">
         <v>18354.3</v>
       </c>
       <c r="I41">
-        <v>90.594999999999999</v>
+        <v>90.595</v>
       </c>
       <c r="K41">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="L41">
         <v>0.626</v>
@@ -3124,51 +3089,51 @@
         <v>695.5</v>
       </c>
       <c r="S41">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T41">
-        <v>8503.7999999999993</v>
+        <v>8503.799999999999</v>
       </c>
       <c r="U41">
-        <v>79.647000000000006</v>
+        <v>79.64700000000001</v>
       </c>
       <c r="W41">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="X41">
-        <v>0.17100000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="Y41">
         <v>1.103</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42">
         <v>1996</v>
       </c>
       <c r="B42">
-        <v>28426.400000000001</v>
+        <v>28426.4</v>
       </c>
       <c r="C42">
-        <v>82.343000000000004</v>
+        <v>82.343</v>
       </c>
       <c r="E42">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="F42">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="G42">
-        <v>0.50800000000000001</v>
+        <v>0.508</v>
       </c>
       <c r="H42">
         <v>18974</v>
       </c>
       <c r="I42">
-        <v>79.066999999999993</v>
+        <v>79.06699999999999</v>
       </c>
       <c r="K42">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="L42">
         <v>0.221</v>
@@ -3183,7 +3148,7 @@
         <v>87.5</v>
       </c>
       <c r="Q42">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="R42">
         <v>0.5</v>
@@ -3195,7 +3160,7 @@
         <v>8667</v>
       </c>
       <c r="U42">
-        <v>80.462000000000003</v>
+        <v>80.462</v>
       </c>
       <c r="W42">
         <v>0.114</v>
@@ -3204,10 +3169,10 @@
         <v>0.125</v>
       </c>
       <c r="Y42">
-        <v>1.5109999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.511</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>1997</v>
       </c>
@@ -3215,31 +3180,31 @@
         <v>28022.3</v>
       </c>
       <c r="C43">
-        <v>91.004000000000005</v>
+        <v>91.004</v>
       </c>
       <c r="E43">
         <v>0.155</v>
       </c>
       <c r="F43">
-        <v>0.55200000000000005</v>
+        <v>0.552</v>
       </c>
       <c r="G43">
-        <v>0.47799999999999998</v>
+        <v>0.478</v>
       </c>
       <c r="H43">
         <v>18169</v>
       </c>
       <c r="I43">
-        <v>93.271000000000001</v>
+        <v>93.271</v>
       </c>
       <c r="K43">
         <v>0.184</v>
       </c>
       <c r="L43">
-        <v>0.66200000000000003</v>
+        <v>0.662</v>
       </c>
       <c r="M43">
-        <v>1.0549999999999999</v>
+        <v>1.055</v>
       </c>
       <c r="N43">
         <v>672.8</v>
@@ -3254,7 +3219,7 @@
         <v>0.6</v>
       </c>
       <c r="S43">
-        <v>0.79100000000000004</v>
+        <v>0.791</v>
       </c>
       <c r="T43">
         <v>9180.5</v>
@@ -3266,13 +3231,13 @@
         <v>0.122</v>
       </c>
       <c r="X43">
-        <v>0.47199999999999998</v>
+        <v>0.472</v>
       </c>
       <c r="Y43">
-        <v>1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>1998</v>
       </c>
@@ -3280,120 +3245,120 @@
         <v>30595</v>
       </c>
       <c r="C44">
-        <v>89.344999999999999</v>
+        <v>89.345</v>
       </c>
       <c r="E44">
         <v>0.13</v>
       </c>
       <c r="F44">
-        <v>0.54800000000000004</v>
+        <v>0.548</v>
       </c>
       <c r="G44">
-        <v>0.52700000000000002</v>
+        <v>0.527</v>
       </c>
       <c r="H44">
         <v>16113</v>
       </c>
       <c r="I44">
-        <v>95.474000000000004</v>
+        <v>95.474</v>
       </c>
       <c r="K44">
         <v>0.157</v>
       </c>
       <c r="L44">
-        <v>0.73299999999999998</v>
+        <v>0.733</v>
       </c>
       <c r="M44">
-        <v>0.90500000000000003</v>
+        <v>0.905</v>
       </c>
       <c r="N44">
         <v>486.9</v>
       </c>
       <c r="S44">
-        <v>0.72899999999999998</v>
+        <v>0.729</v>
       </c>
       <c r="T44">
         <v>13995.1</v>
       </c>
       <c r="U44">
-        <v>86.281000000000006</v>
+        <v>86.28100000000001</v>
       </c>
       <c r="W44">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="X44">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="Y44">
         <v>1.532</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45">
         <v>1999</v>
       </c>
       <c r="B45">
-        <v>27656.400000000001</v>
+        <v>27656.4</v>
       </c>
       <c r="C45">
-        <v>89.813999999999993</v>
+        <v>89.81399999999999</v>
       </c>
       <c r="E45">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="F45">
-        <v>0.54200000000000004</v>
+        <v>0.542</v>
       </c>
       <c r="G45">
-        <v>0.58199999999999996</v>
+        <v>0.582</v>
       </c>
       <c r="H45">
         <v>17390.8</v>
       </c>
       <c r="I45">
-        <v>98.876999999999995</v>
+        <v>98.877</v>
       </c>
       <c r="K45">
         <v>0.151</v>
       </c>
       <c r="L45">
-        <v>0.79700000000000004</v>
+        <v>0.797</v>
       </c>
       <c r="M45">
-        <v>0.73799999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="N45">
         <v>1559.5</v>
       </c>
       <c r="O45">
-        <v>90.191999999999993</v>
+        <v>90.19199999999999</v>
       </c>
       <c r="Q45">
         <v>0.16</v>
       </c>
       <c r="R45">
-        <v>0.57699999999999996</v>
+        <v>0.577</v>
       </c>
       <c r="S45">
-        <v>0.83799999999999997</v>
+        <v>0.838</v>
       </c>
       <c r="T45">
         <v>8706.1</v>
       </c>
       <c r="U45">
-        <v>85.093000000000004</v>
+        <v>85.093</v>
       </c>
       <c r="W45">
-        <v>0.13100000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="X45">
-        <v>0.39600000000000002</v>
+        <v>0.396</v>
       </c>
       <c r="Y45">
-        <v>1.2170000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.217</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>2000</v>
       </c>
@@ -3401,10 +3366,10 @@
         <v>31387.9</v>
       </c>
       <c r="C46">
-        <v>93.903000000000006</v>
+        <v>93.90300000000001</v>
       </c>
       <c r="E46">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="F46">
         <v>0.626</v>
@@ -3422,10 +3387,10 @@
         <v>0.158</v>
       </c>
       <c r="L46">
-        <v>0.73199999999999998</v>
+        <v>0.732</v>
       </c>
       <c r="M46">
-        <v>0.64300000000000002</v>
+        <v>0.643</v>
       </c>
       <c r="N46">
         <v>3041.1</v>
@@ -3446,19 +3411,19 @@
         <v>11107.5</v>
       </c>
       <c r="U46">
-        <v>94.048000000000002</v>
+        <v>94.048</v>
       </c>
       <c r="W46">
         <v>0.184</v>
       </c>
       <c r="X46">
-        <v>0.66700000000000004</v>
+        <v>0.667</v>
       </c>
       <c r="Y46">
         <v>0.97</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47">
         <v>2001</v>
       </c>
@@ -3466,16 +3431,16 @@
         <v>38795.5</v>
       </c>
       <c r="C47">
-        <v>90.108999999999995</v>
+        <v>90.10899999999999</v>
       </c>
       <c r="E47">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="F47">
-        <v>0.51600000000000001</v>
+        <v>0.516</v>
       </c>
       <c r="G47">
-        <v>0.59799999999999998</v>
+        <v>0.598</v>
       </c>
       <c r="H47">
         <v>15834.4</v>
@@ -3484,46 +3449,46 @@
         <v>104.008</v>
       </c>
       <c r="K47">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="L47">
-        <v>0.96099999999999997</v>
+        <v>0.961</v>
       </c>
       <c r="M47">
-        <v>0.73499999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="N47">
         <v>5235.2</v>
       </c>
       <c r="O47">
-        <v>84.594999999999999</v>
+        <v>84.595</v>
       </c>
       <c r="Q47">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="R47">
-        <v>0.40500000000000003</v>
+        <v>0.405</v>
       </c>
       <c r="S47">
         <v>1.371</v>
       </c>
       <c r="T47">
-        <v>17725.900000000001</v>
+        <v>17725.9</v>
       </c>
       <c r="U47">
-        <v>85.917000000000002</v>
+        <v>85.917</v>
       </c>
       <c r="W47">
         <v>0.155</v>
       </c>
       <c r="X47">
-        <v>0.34799999999999998</v>
+        <v>0.348</v>
       </c>
       <c r="Y47">
-        <v>0.56399999999999995</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.5639999999999999</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>2002</v>
       </c>
@@ -3534,43 +3499,43 @@
         <v>84.7</v>
       </c>
       <c r="E48">
-        <v>0.21199999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="F48">
         <v>0.501</v>
       </c>
       <c r="G48">
-        <v>0.56699999999999995</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H48">
         <v>17321</v>
       </c>
       <c r="I48">
-        <v>92.07</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="K48">
-        <v>0.17399999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="L48">
-        <v>0.63200000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="M48">
-        <v>0.54600000000000004</v>
+        <v>0.546</v>
       </c>
       <c r="N48">
-        <v>1142.4000000000001</v>
+        <v>1142.4</v>
       </c>
       <c r="O48">
-        <v>69.736999999999995</v>
+        <v>69.73699999999999</v>
       </c>
       <c r="Q48">
         <v>0.307</v>
       </c>
       <c r="R48">
-        <v>0.23699999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="S48">
-        <v>0.85199999999999998</v>
+        <v>0.852</v>
       </c>
       <c r="T48">
         <v>13282.3</v>
@@ -3582,13 +3547,13 @@
         <v>0.184</v>
       </c>
       <c r="X48">
-        <v>0.56699999999999995</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="Y48">
-        <v>0.45500000000000002</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.455</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>2003</v>
       </c>
@@ -3596,28 +3561,28 @@
         <v>28004.6</v>
       </c>
       <c r="C49">
-        <v>90.183000000000007</v>
+        <v>90.18300000000001</v>
       </c>
       <c r="E49">
-        <v>0.16900000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="F49">
-        <v>0.64400000000000002</v>
+        <v>0.644</v>
       </c>
       <c r="G49">
-        <v>0.50800000000000001</v>
+        <v>0.508</v>
       </c>
       <c r="H49">
         <v>17356</v>
       </c>
       <c r="I49">
-        <v>97.914000000000001</v>
+        <v>97.914</v>
       </c>
       <c r="K49">
         <v>0.128</v>
       </c>
       <c r="L49">
-        <v>0.82699999999999996</v>
+        <v>0.827</v>
       </c>
       <c r="M49">
         <v>0.495</v>
@@ -3626,51 +3591,51 @@
         <v>533.6</v>
       </c>
       <c r="O49">
-        <v>70.525999999999996</v>
+        <v>70.526</v>
       </c>
       <c r="Q49">
         <v>0.27</v>
       </c>
       <c r="R49">
-        <v>0.21099999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="S49">
-        <v>0.89600000000000002</v>
+        <v>0.896</v>
       </c>
       <c r="T49">
         <v>10115</v>
       </c>
       <c r="U49">
-        <v>96.146000000000001</v>
+        <v>96.146</v>
       </c>
       <c r="W49">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="X49">
-        <v>0.76800000000000002</v>
+        <v>0.768</v>
       </c>
       <c r="Y49">
         <v>0.317</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50">
         <v>2004</v>
       </c>
       <c r="B50">
-        <v>22544.799999999999</v>
+        <v>22544.8</v>
       </c>
       <c r="C50">
-        <v>88.396000000000001</v>
+        <v>88.396</v>
       </c>
       <c r="E50">
         <v>0.18</v>
       </c>
       <c r="F50">
-        <v>0.52700000000000002</v>
+        <v>0.527</v>
       </c>
       <c r="G50">
-        <v>0.42799999999999999</v>
+        <v>0.428</v>
       </c>
       <c r="H50">
         <v>13325</v>
@@ -3679,46 +3644,46 @@
         <v>94.12</v>
       </c>
       <c r="K50">
-        <v>0.13100000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="L50">
-        <v>0.69099999999999995</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="M50">
-        <v>0.85099999999999998</v>
+        <v>0.851</v>
       </c>
       <c r="N50">
         <v>703.3</v>
       </c>
       <c r="O50">
-        <v>76.786000000000001</v>
+        <v>76.786</v>
       </c>
       <c r="Q50">
-        <v>0.26800000000000002</v>
+        <v>0.268</v>
       </c>
       <c r="R50">
-        <v>0.32100000000000001</v>
+        <v>0.321</v>
       </c>
       <c r="S50">
-        <v>0.99199999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="T50">
         <v>8516.5</v>
       </c>
       <c r="U50">
-        <v>91.338999999999999</v>
+        <v>91.339</v>
       </c>
       <c r="W50">
         <v>0.16</v>
       </c>
       <c r="X50">
-        <v>0.54700000000000004</v>
+        <v>0.547</v>
       </c>
       <c r="Y50">
-        <v>0.22900000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>2005</v>
       </c>
@@ -3726,22 +3691,22 @@
         <v>18881.5</v>
       </c>
       <c r="C51">
-        <v>91.233000000000004</v>
+        <v>91.233</v>
       </c>
       <c r="E51">
         <v>0.157</v>
       </c>
       <c r="F51">
-        <v>0.56899999999999995</v>
+        <v>0.569</v>
       </c>
       <c r="G51">
-        <v>0.42799999999999999</v>
+        <v>0.428</v>
       </c>
       <c r="H51">
         <v>10772</v>
       </c>
       <c r="I51">
-        <v>94.072999999999993</v>
+        <v>94.07299999999999</v>
       </c>
       <c r="K51">
         <v>0.125</v>
@@ -3750,63 +3715,63 @@
         <v>0.7</v>
       </c>
       <c r="M51">
-        <v>0.81699999999999995</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="N51">
         <v>1446.1</v>
       </c>
       <c r="S51">
-        <v>0.72699999999999998</v>
+        <v>0.727</v>
       </c>
       <c r="T51">
         <v>6663.4</v>
       </c>
       <c r="U51">
-        <v>89.813999999999993</v>
+        <v>89.81399999999999</v>
       </c>
       <c r="W51">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="X51">
         <v>0.504</v>
       </c>
       <c r="Y51">
-        <v>0.14499999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2006</v>
       </c>
       <c r="B52">
-        <v>24452.799999999999</v>
+        <v>24452.8</v>
       </c>
       <c r="C52">
-        <v>90.891999999999996</v>
+        <v>90.892</v>
       </c>
       <c r="E52">
-        <v>0.16300000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="F52">
-        <v>0.61199999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="G52">
-        <v>0.45100000000000001</v>
+        <v>0.451</v>
       </c>
       <c r="H52">
         <v>12359</v>
       </c>
       <c r="I52">
-        <v>91.456999999999994</v>
+        <v>91.45699999999999</v>
       </c>
       <c r="K52">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="L52">
-        <v>0.59699999999999998</v>
+        <v>0.597</v>
       </c>
       <c r="M52">
-        <v>0.66100000000000003</v>
+        <v>0.661</v>
       </c>
       <c r="N52">
         <v>2247.1</v>
@@ -3815,22 +3780,22 @@
         <v>0.41</v>
       </c>
       <c r="T52">
-        <v>9846.7000000000007</v>
+        <v>9846.700000000001</v>
       </c>
       <c r="U52">
         <v>90.61</v>
       </c>
       <c r="W52">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="X52">
-        <v>0.61899999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="Y52">
-        <v>0.56100000000000005</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.5610000000000001</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53">
         <v>2007</v>
       </c>
@@ -3838,96 +3803,96 @@
         <v>20283</v>
       </c>
       <c r="C53">
-        <v>86.751000000000005</v>
+        <v>86.751</v>
       </c>
       <c r="E53">
         <v>0.159</v>
       </c>
       <c r="F53">
-        <v>0.45600000000000002</v>
+        <v>0.456</v>
       </c>
       <c r="G53">
-        <v>0.48699999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="H53">
         <v>13202</v>
       </c>
       <c r="I53">
-        <v>90.319000000000003</v>
+        <v>90.319</v>
       </c>
       <c r="K53">
         <v>0.153</v>
       </c>
       <c r="L53">
-        <v>0.57899999999999996</v>
+        <v>0.579</v>
       </c>
       <c r="M53">
-        <v>0.83299999999999996</v>
+        <v>0.833</v>
       </c>
       <c r="N53">
         <v>1313.5</v>
       </c>
       <c r="O53">
-        <v>87.082999999999998</v>
+        <v>87.083</v>
       </c>
       <c r="Q53">
         <v>0.186</v>
       </c>
       <c r="R53">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="S53">
-        <v>0.35099999999999998</v>
+        <v>0.351</v>
       </c>
       <c r="T53">
         <v>5767.5</v>
       </c>
       <c r="U53">
-        <v>84.801000000000002</v>
+        <v>84.801</v>
       </c>
       <c r="W53">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="X53">
-        <v>0.41399999999999998</v>
+        <v>0.414</v>
       </c>
       <c r="Y53">
-        <v>0.70599999999999996</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.706</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54">
         <v>2008</v>
       </c>
       <c r="B54">
-        <v>18867.400000000001</v>
+        <v>18867.4</v>
       </c>
       <c r="C54">
-        <v>89.019000000000005</v>
+        <v>89.01900000000001</v>
       </c>
       <c r="E54">
         <v>0.157</v>
       </c>
       <c r="F54">
-        <v>0.48399999999999999</v>
+        <v>0.484</v>
       </c>
       <c r="G54">
-        <v>0.51400000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="H54">
-        <v>10054.200000000001</v>
+        <v>10054.2</v>
       </c>
       <c r="I54">
-        <v>88.051000000000002</v>
+        <v>88.051</v>
       </c>
       <c r="K54">
         <v>0.153</v>
       </c>
       <c r="L54">
-        <v>0.48699999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="M54">
-        <v>0.90200000000000002</v>
+        <v>0.902</v>
       </c>
       <c r="N54">
         <v>2632.8</v>
@@ -3936,13 +3901,13 @@
         <v>94</v>
       </c>
       <c r="Q54">
-        <v>0.20200000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="R54">
-        <v>0.46700000000000003</v>
+        <v>0.467</v>
       </c>
       <c r="S54">
-        <v>0.61899999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="T54">
         <v>6180.4</v>
@@ -3951,16 +3916,16 @@
         <v>87.012</v>
       </c>
       <c r="W54">
-        <v>0.13600000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="X54">
-        <v>0.49099999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="Y54">
-        <v>0.53100000000000003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.531</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55">
         <v>2009</v>
       </c>
@@ -3968,16 +3933,16 @@
         <v>22248.3</v>
       </c>
       <c r="C55">
-        <v>92.085999999999999</v>
+        <v>92.086</v>
       </c>
       <c r="E55">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="F55">
         <v>0.61</v>
       </c>
       <c r="G55">
-        <v>0.47599999999999998</v>
+        <v>0.476</v>
       </c>
       <c r="H55">
         <v>9052</v>
@@ -3986,13 +3951,13 @@
         <v>90.863</v>
       </c>
       <c r="K55">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="L55">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="M55">
-        <v>0.99199999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="N55">
         <v>2470.4</v>
@@ -4001,63 +3966,63 @@
         <v>100.851</v>
       </c>
       <c r="Q55">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="R55">
-        <v>0.93600000000000005</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="S55">
-        <v>0.81599999999999995</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="T55">
         <v>10725.9</v>
       </c>
       <c r="U55">
-        <v>88.314999999999998</v>
+        <v>88.315</v>
       </c>
       <c r="W55">
         <v>0.157</v>
       </c>
       <c r="X55">
-        <v>0.46800000000000003</v>
+        <v>0.468</v>
       </c>
       <c r="Y55">
-        <v>0.67100000000000004</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.671</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56">
         <v>2010</v>
       </c>
       <c r="B56">
-        <v>19224.599999999999</v>
+        <v>19224.6</v>
       </c>
       <c r="C56">
-        <v>91.075000000000003</v>
+        <v>91.075</v>
       </c>
       <c r="E56">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="F56">
-        <v>0.55900000000000005</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G56">
-        <v>0.48799999999999999</v>
+        <v>0.488</v>
       </c>
       <c r="H56">
         <v>11104.7</v>
       </c>
       <c r="I56">
-        <v>93.025000000000006</v>
+        <v>93.02500000000001</v>
       </c>
       <c r="K56">
         <v>0.15</v>
       </c>
       <c r="L56">
-        <v>0.61399999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="M56">
-        <v>1.0289999999999999</v>
+        <v>1.029</v>
       </c>
       <c r="N56">
         <v>1693.2</v>
@@ -4066,31 +4031,31 @@
         <v>101.429</v>
       </c>
       <c r="Q56">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="R56">
-        <v>0.95199999999999996</v>
+        <v>0.952</v>
       </c>
       <c r="S56">
-        <v>1.0609999999999999</v>
+        <v>1.061</v>
       </c>
       <c r="T56">
         <v>6426.7</v>
       </c>
       <c r="U56">
-        <v>84.923000000000002</v>
+        <v>84.923</v>
       </c>
       <c r="W56">
         <v>0.151</v>
       </c>
       <c r="X56">
-        <v>0.33600000000000002</v>
+        <v>0.336</v>
       </c>
       <c r="Y56">
-        <v>0.58899999999999997</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.589</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57">
         <v>2011</v>
       </c>
@@ -4104,58 +4069,58 @@
         <v>0.151</v>
       </c>
       <c r="F57">
-        <v>0.57299999999999995</v>
+        <v>0.573</v>
       </c>
       <c r="G57">
-        <v>0.55400000000000005</v>
+        <v>0.554</v>
       </c>
       <c r="H57">
         <v>13102.6</v>
       </c>
       <c r="I57">
-        <v>92.960999999999999</v>
+        <v>92.961</v>
       </c>
       <c r="K57">
         <v>0.159</v>
       </c>
       <c r="L57">
-        <v>0.57699999999999996</v>
+        <v>0.577</v>
       </c>
       <c r="M57">
-        <v>0.89200000000000002</v>
+        <v>0.892</v>
       </c>
       <c r="N57">
         <v>1888.5</v>
       </c>
       <c r="O57">
-        <v>86.971999999999994</v>
+        <v>86.97199999999999</v>
       </c>
       <c r="Q57">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="R57">
-        <v>0.45100000000000001</v>
+        <v>0.451</v>
       </c>
       <c r="S57">
-        <v>0.82699999999999996</v>
+        <v>0.827</v>
       </c>
       <c r="T57">
         <v>9134.9</v>
       </c>
       <c r="U57">
-        <v>93.051000000000002</v>
+        <v>93.051</v>
       </c>
       <c r="W57">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="X57">
-        <v>0.63200000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="Y57">
         <v>0.371</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58">
         <v>2012</v>
       </c>
@@ -4163,16 +4128,16 @@
         <v>25272.2</v>
       </c>
       <c r="C58">
-        <v>87.29</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E58">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="F58">
-        <v>0.42699999999999999</v>
+        <v>0.427</v>
       </c>
       <c r="G58">
-        <v>0.59499999999999997</v>
+        <v>0.595</v>
       </c>
       <c r="H58">
         <v>12902.3</v>
@@ -4184,25 +4149,25 @@
         <v>0.128</v>
       </c>
       <c r="L58">
-        <v>0.52200000000000002</v>
+        <v>0.522</v>
       </c>
       <c r="M58">
-        <v>0.96899999999999997</v>
+        <v>0.969</v>
       </c>
       <c r="N58">
         <v>3707.6</v>
       </c>
       <c r="O58">
-        <v>84.537999999999997</v>
+        <v>84.538</v>
       </c>
       <c r="Q58">
         <v>0.127</v>
       </c>
       <c r="R58">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="T58">
-        <v>8662.2999999999993</v>
+        <v>8662.299999999999</v>
       </c>
       <c r="U58">
         <v>87.503</v>
@@ -4211,69 +4176,69 @@
         <v>0.155</v>
       </c>
       <c r="X58">
-        <v>0.46200000000000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.462</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59">
         <v>2013</v>
       </c>
       <c r="B59">
-        <v>19423.900000000001</v>
+        <v>19423.9</v>
       </c>
       <c r="C59">
-        <v>89.557000000000002</v>
+        <v>89.557</v>
       </c>
       <c r="E59">
         <v>0.13</v>
       </c>
       <c r="F59">
-        <v>0.57599999999999996</v>
+        <v>0.576</v>
       </c>
       <c r="G59">
-        <v>0.61299999999999999</v>
+        <v>0.613</v>
       </c>
       <c r="H59">
-        <v>8552.2000000000007</v>
+        <v>8552.200000000001</v>
       </c>
       <c r="I59">
-        <v>88.572999999999993</v>
+        <v>88.57299999999999</v>
       </c>
       <c r="K59">
         <v>0.13</v>
       </c>
       <c r="L59">
-        <v>0.46899999999999997</v>
+        <v>0.469</v>
       </c>
       <c r="M59">
-        <v>0.89300000000000002</v>
+        <v>0.893</v>
       </c>
       <c r="N59">
-        <v>4136.1000000000004</v>
+        <v>4136.1</v>
       </c>
       <c r="O59">
-        <v>88.078999999999994</v>
+        <v>88.07899999999999</v>
       </c>
       <c r="Q59">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="R59">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="T59">
         <v>6735.6</v>
       </c>
       <c r="U59">
-        <v>90.376999999999995</v>
+        <v>90.377</v>
       </c>
       <c r="W59">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="X59">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60">
         <v>2014</v>
       </c>
@@ -4281,37 +4246,37 @@
         <v>13722.7</v>
       </c>
       <c r="C60">
-        <v>86.085999999999999</v>
+        <v>86.086</v>
       </c>
       <c r="E60">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="F60">
         <v>0.32</v>
       </c>
       <c r="G60">
-        <v>0.58099999999999996</v>
+        <v>0.581</v>
       </c>
       <c r="H60">
         <v>6677.3</v>
       </c>
       <c r="I60">
-        <v>85.933000000000007</v>
+        <v>85.93300000000001</v>
       </c>
       <c r="K60">
-        <v>0.13900000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="L60">
-        <v>0.33100000000000002</v>
+        <v>0.331</v>
       </c>
       <c r="M60">
-        <v>0.71599999999999997</v>
+        <v>0.716</v>
       </c>
       <c r="N60">
         <v>1646.8</v>
       </c>
       <c r="O60">
-        <v>85.126000000000005</v>
+        <v>85.126</v>
       </c>
       <c r="Q60">
         <v>0.105</v>
@@ -4323,16 +4288,16 @@
         <v>5398.6</v>
       </c>
       <c r="U60">
-        <v>86.641999999999996</v>
+        <v>86.642</v>
       </c>
       <c r="W60">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="X60">
-        <v>0.38200000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.382</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61">
         <v>2015</v>
       </c>
@@ -4340,25 +4305,25 @@
         <v>15200.7</v>
       </c>
       <c r="C61">
-        <v>88.516999999999996</v>
+        <v>88.517</v>
       </c>
       <c r="E61">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="F61">
-        <v>0.51400000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="G61">
-        <v>0.54400000000000004</v>
+        <v>0.544</v>
       </c>
       <c r="H61">
         <v>7160.8</v>
       </c>
       <c r="I61">
-        <v>91.29</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="K61">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="L61">
         <v>0.626</v>
@@ -4370,10 +4335,10 @@
         <v>2326.9</v>
       </c>
       <c r="O61">
-        <v>89.879000000000005</v>
+        <v>89.879</v>
       </c>
       <c r="Q61">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="R61">
         <v>0.621</v>
@@ -4382,16 +4347,16 @@
         <v>5713</v>
       </c>
       <c r="U61">
-        <v>86.448999999999998</v>
+        <v>86.449</v>
       </c>
       <c r="W61">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="X61">
-        <v>0.40300000000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.403</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62">
         <v>2016</v>
       </c>
@@ -4399,19 +4364,19 @@
         <v>14383.1</v>
       </c>
       <c r="C62">
-        <v>91.177000000000007</v>
+        <v>91.17700000000001</v>
       </c>
       <c r="E62">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="F62">
-        <v>0.66900000000000004</v>
+        <v>0.669</v>
       </c>
       <c r="G62">
-        <v>0.55200000000000005</v>
+        <v>0.552</v>
       </c>
       <c r="H62">
-        <v>8955.2999999999993</v>
+        <v>8955.299999999999</v>
       </c>
       <c r="I62">
         <v>92.759</v>
@@ -4420,7 +4385,7 @@
         <v>0.107</v>
       </c>
       <c r="L62">
-        <v>0.70699999999999996</v>
+        <v>0.707</v>
       </c>
       <c r="M62">
         <v>1.143</v>
@@ -4429,28 +4394,28 @@
         <v>1501.9</v>
       </c>
       <c r="O62">
-        <v>92.192999999999998</v>
+        <v>92.193</v>
       </c>
       <c r="Q62">
-        <v>8.4000000000000005E-2</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="R62">
-        <v>0.73099999999999998</v>
+        <v>0.731</v>
       </c>
       <c r="T62">
         <v>3925.9</v>
       </c>
       <c r="U62">
-        <v>88.576999999999998</v>
+        <v>88.577</v>
       </c>
       <c r="W62">
         <v>0.113</v>
       </c>
       <c r="X62">
-        <v>0.56899999999999995</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.569</v>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63">
         <v>2017</v>
       </c>
@@ -4458,58 +4423,58 @@
         <v>13824.6</v>
       </c>
       <c r="C63">
-        <v>91.537999999999997</v>
+        <v>91.538</v>
       </c>
       <c r="E63">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="F63">
-        <v>0.69299999999999995</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G63">
-        <v>0.63100000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="H63">
         <v>9176</v>
       </c>
       <c r="I63">
-        <v>93.254000000000005</v>
+        <v>93.254</v>
       </c>
       <c r="K63">
         <v>0.106</v>
       </c>
       <c r="L63">
-        <v>0.74099999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="M63">
-        <v>1.0289999999999999</v>
+        <v>1.029</v>
       </c>
       <c r="N63">
         <v>1743.1</v>
       </c>
       <c r="O63">
-        <v>86.099000000000004</v>
+        <v>86.099</v>
       </c>
       <c r="Q63">
         <v>0.104</v>
       </c>
       <c r="R63">
-        <v>0.31900000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="T63">
         <v>2905.5</v>
       </c>
       <c r="U63">
-        <v>93.4</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="W63">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="X63">
-        <v>0.85599999999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.856</v>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64">
         <v>2018</v>
       </c>
@@ -4517,28 +4482,28 @@
         <v>17045.5</v>
       </c>
       <c r="C64">
-        <v>92.984999999999999</v>
+        <v>92.985</v>
       </c>
       <c r="E64">
         <v>0.112</v>
       </c>
       <c r="F64">
-        <v>0.71099999999999997</v>
+        <v>0.711</v>
       </c>
       <c r="G64">
-        <v>0.80300000000000005</v>
+        <v>0.803</v>
       </c>
       <c r="H64">
         <v>9393.6</v>
       </c>
       <c r="I64">
-        <v>96.177999999999997</v>
+        <v>96.178</v>
       </c>
       <c r="K64">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="L64">
-        <v>0.80300000000000005</v>
+        <v>0.803</v>
       </c>
       <c r="M64">
         <v>1.284</v>
@@ -4547,25 +4512,25 @@
         <v>3517.8</v>
       </c>
       <c r="O64">
-        <v>89.257999999999996</v>
+        <v>89.258</v>
       </c>
       <c r="Q64">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="R64">
-        <v>0.66800000000000004</v>
+        <v>0.668</v>
       </c>
       <c r="T64">
-        <v>4134.1000000000004</v>
+        <v>4134.1</v>
       </c>
       <c r="U64">
-        <v>93.251999999999995</v>
+        <v>93.252</v>
       </c>
       <c r="W64">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="X64">
-        <v>0.68700000000000006</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/Albacore_SAtl.xlsx
+++ b/Indicator_4/Real_data/Albacore_SAtl.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>0.608</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4536,4 +4537,850 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C64"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1956</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>5.184644581938251</v>
+      </c>
+      <c r="C2">
+        <v>0.7146626344293407</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1957</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>5.184150838592214</v>
+      </c>
+      <c r="C3">
+        <v>0.7146626344293407</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1958</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>5.167270987949577</v>
+      </c>
+      <c r="C4">
+        <v>0.714693493388468</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1959</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>5.144435358195368</v>
+      </c>
+      <c r="C5">
+        <v>0.714681149804817</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1960</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>5.038866859020845</v>
+      </c>
+      <c r="C6">
+        <v>0.714258382064773</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_1961</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>4.802302078350897</v>
+      </c>
+      <c r="C7">
+        <v>0.6583080032710497</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_1962</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4.582617148323587</v>
+      </c>
+      <c r="C8">
+        <v>0.57430374473469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_1963</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>4.210612396043881</v>
+      </c>
+      <c r="C9">
+        <v>0.4866087546867044</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_1964</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>3.930135316535773</v>
+      </c>
+      <c r="C10">
+        <v>0.4143062134514203</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_1965</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>3.518415083859221</v>
+      </c>
+      <c r="C11">
+        <v>0.3579299810217401</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_1966</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>3.133264414991282</v>
+      </c>
+      <c r="C12">
+        <v>0.3784974772800913</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_1967</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2.916591319374798</v>
+      </c>
+      <c r="C13">
+        <v>0.449510114023854</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_1968</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2.975578219746648</v>
+      </c>
+      <c r="C14">
+        <v>0.5096696548425421</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_1969</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2.844100538488837</v>
+      </c>
+      <c r="C15">
+        <v>0.5427319436515406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_1970</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2.628322352687044</v>
+      </c>
+      <c r="C16">
+        <v>0.5450741386493034</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_1971</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2.481544799493913</v>
+      </c>
+      <c r="C17">
+        <v>0.5240314144203916</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_1972</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2.292928669515977</v>
+      </c>
+      <c r="C18">
+        <v>0.4954930490194566</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_1973</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>1.9527086451374</v>
+      </c>
+      <c r="C19">
+        <v>0.4581938251222786</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_1974</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1.767474657079817</v>
+      </c>
+      <c r="C20">
+        <v>0.4254678989677678</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_1975</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1.778809152767277</v>
+      </c>
+      <c r="C21">
+        <v>0.4066130749409823</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_1976</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1.827467559519217</v>
+      </c>
+      <c r="C22">
+        <v>0.3969171899831818</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_1977</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.838518152782707</v>
+      </c>
+      <c r="C23">
+        <v>0.3916001913255466</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_1978</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1.825008100476771</v>
+      </c>
+      <c r="C24">
+        <v>0.3890666707811946</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_1979</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1.802703244819552</v>
+      </c>
+      <c r="C25">
+        <v>0.3859252287420346</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_1980</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1.791859406582216</v>
+      </c>
+      <c r="C26">
+        <v>0.3797596087083983</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_1981</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>1.771865886963633</v>
+      </c>
+      <c r="C27">
+        <v>0.3688324512814183</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SSB_1982</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1.709277746061625</v>
+      </c>
+      <c r="C28">
+        <v>0.3553378284550462</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SSB_1983</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1.518637268364938</v>
+      </c>
+      <c r="C29">
+        <v>0.3405779883044545</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSB_1984</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>1.613327984447084</v>
+      </c>
+      <c r="C30">
+        <v>0.3380598972396661</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SSB_1985</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>1.747474965669408</v>
+      </c>
+      <c r="C31">
+        <v>0.3334557405378716</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SSB_1986</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>1.602959374180309</v>
+      </c>
+      <c r="C32">
+        <v>0.3154865686380399</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SSB_1987</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>1.390155992038388</v>
+      </c>
+      <c r="C33">
+        <v>0.2915829103084353</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SSB_1988</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1.157223310857725</v>
+      </c>
+      <c r="C34">
+        <v>0.2672246995108855</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SSB_1989</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>1.097094628998164</v>
+      </c>
+      <c r="C35">
+        <v>0.2569903257163136</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SSB_1990</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>1.125151594636713</v>
+      </c>
+      <c r="C36">
+        <v>0.252213050253815</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SSB_1991</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1.164138803598155</v>
+      </c>
+      <c r="C37">
+        <v>0.2478153399885822</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SSB_1992</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>1.243529647744982</v>
+      </c>
+      <c r="C38">
+        <v>0.2470910802178642</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SSB_1993</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>1.1533875422382</v>
+      </c>
+      <c r="C39">
+        <v>0.2372625017358165</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SSB_1994</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1.098248754069525</v>
+      </c>
+      <c r="C40">
+        <v>0.2324358519387141</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1.033404823255312</v>
+      </c>
+      <c r="C41">
+        <v>0.2284630695406644</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1.140883491999815</v>
+      </c>
+      <c r="C42">
+        <v>0.2380558855749796</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1.257962382928824</v>
+      </c>
+      <c r="C43">
+        <v>0.2475234142352379</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>1.341800003085896</v>
+      </c>
+      <c r="C44">
+        <v>0.253380444677601</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1.292907068244588</v>
+      </c>
+      <c r="C45">
+        <v>0.2536933545231519</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1.225433954112728</v>
+      </c>
+      <c r="C46">
+        <v>0.2504284766474827</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1.098436993720202</v>
+      </c>
+      <c r="C47">
+        <v>0.2387659502244989</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0.9253737791424296</v>
+      </c>
+      <c r="C48">
+        <v>0.2191985928314638</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.9268827822437549</v>
+      </c>
+      <c r="C49">
+        <v>0.2059746030766382</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>0.9752418570921603</v>
+      </c>
+      <c r="C50">
+        <v>0.1984132323216738</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1.053771736279335</v>
+      </c>
+      <c r="C51">
+        <v>0.202069093209486</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>1.111579824412523</v>
+      </c>
+      <c r="C52">
+        <v>0.2105864745182145</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>1.029880730122973</v>
+      </c>
+      <c r="C53">
+        <v>0.215374859205999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>1.054947462622086</v>
+      </c>
+      <c r="C54">
+        <v>0.2245572510839209</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>1.197886161299779</v>
+      </c>
+      <c r="C55">
+        <v>0.237664285383654</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>1.28779065282128</v>
+      </c>
+      <c r="C56">
+        <v>0.2486908086590239</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>1.326802548950024</v>
+      </c>
+      <c r="C57">
+        <v>0.2602055206677879</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>1.257058215426394</v>
+      </c>
+      <c r="C58">
+        <v>0.2690194565737297</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>1.176494730832729</v>
+      </c>
+      <c r="C59">
+        <v>0.2783783616978599</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>1.19294872783941</v>
+      </c>
+      <c r="C60">
+        <v>0.2926935242474271</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>1.365484254216105</v>
+      </c>
+      <c r="C61">
+        <v>0.3193531962166916</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>1.737313110428785</v>
+      </c>
+      <c r="C62">
+        <v>0.3721621329712549</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>2.044152998719353</v>
+      </c>
+      <c r="C63">
+        <v>0.4187961920044437</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SSB_2018</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>2.197697921649103</v>
+      </c>
+      <c r="C64">
+        <v>0.4463100399623521</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>